--- a/clients/febal-casa/catalog.xlsx
+++ b/clients/febal-casa/catalog.xlsx
@@ -463,10 +463,10 @@
         <v>Boiserie camino</v>
       </c>
       <c r="C2" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D2" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -475,7 +475,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>boiserie, camino, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, camino, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -505,7 +505,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q2" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R2" t="str">
         <v>TRUE</v>
@@ -519,10 +519,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C3" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D3" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -531,7 +531,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -561,7 +561,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q3" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R3" t="str">
         <v>TRUE</v>
@@ -575,7 +575,7 @@
         <v>Divano Balmoral</v>
       </c>
       <c r="C4" t="str">
-        <v>sofás</v>
+        <v>divani</v>
       </c>
       <c r="D4" t="str">
         <v>Un divano componibile pensato per interpretare le esigenze abitative contemporanee, coniugando estetica, ergonomia e versatilità. La scelta ideale per un soggiorno elegante, accogliente e su misura.</v>
@@ -587,7 +587,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>divano, balmoral, sofás, sofa, sofá, couch, asiento, componibile, pensato, interpretare, esigenze, abitative, contemporanee, coniugando, estetica, ergonomia, versatilita, scelta</v>
+        <v>divano, balmoral, divani, sofa, sofá, sofás, couch, asiento, componibile, pensato, interpretare, esigenze, abitative, contemporanee, coniugando, estetica, ergonomia, versatilita, scelta</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -617,7 +617,7 @@
         <v>https://www.febalcasa.com/it/prodotti/balmoral/</v>
       </c>
       <c r="Q4" t="str">
-        <v>sofas</v>
+        <v>divani</v>
       </c>
       <c r="R4" t="str">
         <v>TRUE</v>
@@ -631,10 +631,10 @@
         <v>Tavolino Rio</v>
       </c>
       <c r="C5" t="str">
-        <v>mesas de centro</v>
+        <v>tavolini</v>
       </c>
       <c r="D5" t="str">
-        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende</v>
+        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -643,7 +643,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>tavolino, rio, mesas de centro, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
+        <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.febalcasa.com/it/prodotti/rio/</v>
       </c>
       <c r="Q5" t="str">
-        <v>mesas-de-centro</v>
+        <v>tavolini</v>
       </c>
       <c r="R5" t="str">
         <v>TRUE</v>
@@ -687,10 +687,10 @@
         <v>Tavolino Rio</v>
       </c>
       <c r="C6" t="str">
-        <v>mesas de centro</v>
+        <v>tavolini</v>
       </c>
       <c r="D6" t="str">
-        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende</v>
+        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -699,7 +699,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>tavolino, rio, mesas de centro, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
+        <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -729,7 +729,7 @@
         <v>https://www.febalcasa.com/it/prodotti/rio/</v>
       </c>
       <c r="Q6" t="str">
-        <v>mesas-de-centro</v>
+        <v>tavolini</v>
       </c>
       <c r="R6" t="str">
         <v>TRUE</v>
@@ -743,10 +743,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C7" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D7" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -785,7 +785,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q7" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R7" t="str">
         <v>TRUE</v>
@@ -799,7 +799,7 @@
         <v>Cucina Origina Anta Square Cannettato</v>
       </c>
       <c r="C8" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D8" t="str">
         <v>Cucina Origina Anta Square Cannettato — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
@@ -811,7 +811,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>cucina, origina, anta, square, cannettato, cocinas, cocina, kitchen, isla, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>cucina, origina, anta, square, cannettato, cucine, cocina, cocinas, kitchen, isla, casa, pieza, coleccion, febal, seccion, autentica</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -841,7 +841,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-square-cannettato/</v>
       </c>
       <c r="Q8" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R8" t="str">
         <v>TRUE</v>
@@ -855,7 +855,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C9" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D9" t="str">
         <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
@@ -867,7 +867,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-square-cannettato/</v>
       </c>
       <c r="Q9" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R9" t="str">
         <v>TRUE</v>
@@ -911,7 +911,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C10" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D10" t="str">
         <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
@@ -923,7 +923,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -953,7 +953,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-square-cannettato/</v>
       </c>
       <c r="Q10" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R10" t="str">
         <v>TRUE</v>
@@ -967,7 +967,7 @@
         <v>Sistema Diciotto</v>
       </c>
       <c r="C11" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D11" t="str">
         <v>Diciotto è una parete attrezzata per la zona living di design: pratico, versatile e funzionale permette una modularità altissima.</v>
@@ -979,7 +979,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>sistema, diciotto, sistemas modulares, sistema modular, modular, parete, attrezzata, zona, living, design, pratico, versatile, funzionale, permette, modularita, altissima</v>
+        <v>sistema, diciotto, sistemi modulari, sistema modular, sistemas modulares, modular, parete, attrezzata, zona, living, design, pratico, versatile, funzionale, permette, modularita, altissima</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>https://www.febalcasa.com/it/prodotti/diciotto/</v>
       </c>
       <c r="Q11" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R11" t="str">
         <v>TRUE</v>
@@ -1023,7 +1023,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C12" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D12" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -1035,7 +1035,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -1065,7 +1065,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q12" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R12" t="str">
         <v>TRUE</v>
@@ -1079,7 +1079,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C13" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D13" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -1091,7 +1091,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -1121,7 +1121,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q13" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R13" t="str">
         <v>TRUE</v>
@@ -1135,7 +1135,7 @@
         <v>Madie Aurora</v>
       </c>
       <c r="C14" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="D14" t="str">
         <v>La madia Aurora si distingue per la leggerezza dei volumi e l’estetica ricercata. Arreda la tua Casa con Febal Casa.</v>
@@ -1147,7 +1147,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>madie, aurora, aparadores, aparador, madia, credenza, sideboard, buffet, casa, distingue, leggerezza, volumi, estetica, ricercata, arreda, febal</v>
+        <v>madie, aurora, aparador, aparadores, madia, credenza, sideboard, buffet, casa, distingue, leggerezza, volumi, estetica, ricercata, arreda, febal</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -1177,7 +1177,7 @@
         <v>https://www.febalcasa.com/it/prodotti/aurora/</v>
       </c>
       <c r="Q14" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="R14" t="str">
         <v>TRUE</v>
@@ -1191,10 +1191,10 @@
         <v>Tavolino Rio</v>
       </c>
       <c r="C15" t="str">
-        <v>mesas de centro</v>
+        <v>tavolini</v>
       </c>
       <c r="D15" t="str">
-        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende</v>
+        <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1203,7 +1203,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>tavolino, rio, mesas de centro, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
+        <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1233,7 +1233,7 @@
         <v>https://www.febalcasa.com/it/prodotti/rio/</v>
       </c>
       <c r="Q15" t="str">
-        <v>mesas-de-centro</v>
+        <v>tavolini</v>
       </c>
       <c r="R15" t="str">
         <v>TRUE</v>
@@ -1247,7 +1247,7 @@
         <v>Armadio Profile/ Block</v>
       </c>
       <c r="C16" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D16" t="str">
         <v>L'armadio con anta battente Profile Block si distingue per le sue linee nette e moderne, perfetta per un armadio dal carattere deciso.</v>
@@ -1259,7 +1259,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>armadio, profile/, block, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, distingue, linee, nette, moderne, perfetta, carattere, deciso</v>
+        <v>armadio, profile/, block, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, distingue, linee, nette, moderne, perfetta, carattere, deciso</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1289,7 +1289,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-block/</v>
       </c>
       <c r="Q16" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R16" t="str">
         <v>TRUE</v>
@@ -1303,10 +1303,10 @@
         <v>Libreria Lapis</v>
       </c>
       <c r="C17" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D17" t="str">
-        <v>Il sistema libreria Lapis, configurabile a parete e centro stanza, si adatta perfettamente anche ad ambienti giorno e notte regalando estremo rigore e</v>
+        <v>Il sistema libreria Lapis, configurabile a parete e centro stanza, si adatta perfettamente anche ad ambienti giorno e notte regalando estremo rigore e contenimento. Il suo design inedito è personalizzabile grazie a diversi elementi compositivi: ripiani in vetro, in metallo o in pannello, pensili e basi in differenti modularità per soddisfare qualsiasi esigenza.</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1315,7 +1315,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>libreria, lapis, librerías, librería, estanteria, estantería, bookshelf, estante, sistema, configurabile, parete, centro, stanza, adatta, perfettamente, ambienti, giorno, notte</v>
+        <v>libreria, lapis, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, sistema, configurabile, parete, centro, stanza, adatta, perfettamente, ambienti, giorno, notte</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1345,7 +1345,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lapis/</v>
       </c>
       <c r="Q17" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R17" t="str">
         <v>TRUE</v>
@@ -1359,10 +1359,10 @@
         <v>Pouff Windsor</v>
       </c>
       <c r="C18" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="D18" t="str">
-        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento</v>
+        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento estremamente versatile che risponde a qualsiasi esigenza. La sua leggerezza permette di offrire soluzioni dinamiche per ogni stile di vita.</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1371,7 +1371,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>pouff, windsor, puffs, puff, puf, ottoman, reposapies, pouf, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
+        <v>pouff, windsor, pouf, puff, puffs, puf, ottoman, reposapies, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1401,7 +1401,7 @@
         <v>https://www.febalcasa.com/it/prodotti/windsor/</v>
       </c>
       <c r="Q18" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="R18" t="str">
         <v>TRUE</v>
@@ -1415,10 +1415,10 @@
         <v>Boiserie TV</v>
       </c>
       <c r="C19" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D19" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1457,7 +1457,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q19" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R19" t="str">
         <v>TRUE</v>
@@ -1471,7 +1471,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C20" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D20" t="str">
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1513,7 +1513,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-telaio-legno/</v>
       </c>
       <c r="Q20" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R20" t="str">
         <v>TRUE</v>
@@ -1527,7 +1527,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C21" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D21" t="str">
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
@@ -1539,7 +1539,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1569,7 +1569,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-telaio-legno/</v>
       </c>
       <c r="Q21" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R21" t="str">
         <v>TRUE</v>
@@ -1583,7 +1583,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C22" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D22" t="str">
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
@@ -1595,7 +1595,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1625,7 +1625,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-telaio-legno/</v>
       </c>
       <c r="Q22" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R22" t="str">
         <v>TRUE</v>
@@ -1639,7 +1639,7 @@
         <v>Armadio Barret con Portale</v>
       </c>
       <c r="C23" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D23" t="str">
         <v>Scopri gli armadi a ponte con passaggio Febal Casa: soluzioni architettoniche che ottimizzano lo spazio con stile e funzionalità.</v>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>armadio, barret, portale, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, scopri, armadi, ponte, passaggio, febal, casa, soluzioni, architettoniche, ottimizzano, spazio, stile, funzionalita</v>
+        <v>armadio, barret, portale, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, scopri, ponte, passaggio, febal, casa, soluzioni, architettoniche, ottimizzano, spazio, stile, funzionalita</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1681,7 +1681,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ispirazioni/armadio-con-passaggio-con-ponte/</v>
       </c>
       <c r="Q23" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R23" t="str">
         <v>TRUE</v>
@@ -1695,7 +1695,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C24" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D24" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -1707,7 +1707,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q24" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R24" t="str">
         <v>TRUE</v>
@@ -1751,10 +1751,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C25" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D25" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1763,7 +1763,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1793,7 +1793,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q25" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R25" t="str">
         <v>TRUE</v>
@@ -1807,7 +1807,7 @@
         <v>Libreria Trenta Anta Libeskind022</v>
       </c>
       <c r="C26" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D26" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>libreria, trenta, anta, libeskind022, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, anta, libeskind022, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1849,7 +1849,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q26" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R26" t="str">
         <v>TRUE</v>
@@ -1863,7 +1863,7 @@
         <v>Divano Camden</v>
       </c>
       <c r="C27" t="str">
-        <v>sofás</v>
+        <v>divani</v>
       </c>
       <c r="D27" t="str">
         <v>Camden unisce eleganza e comfort in un design armonioso e avvolgente. Personalizzabile nei rivestimenti, si adatta a spazi classici e moderni, offrendo stile, calore e funzionalità a ogni ambiente living.</v>
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>divano, camden, sofás, sofa, sofá, couch, asiento, unisce, eleganza, comfort, design, armonioso, avvolgente, personalizzabile, rivestimenti, adatta, spazi, classici</v>
+        <v>divano, camden, divani, sofa, sofá, sofás, couch, asiento, unisce, eleganza, comfort, design, armonioso, avvolgente, personalizzabile, rivestimenti, adatta, spazi, classici</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1905,7 +1905,7 @@
         <v>https://www.febalcasa.com/it/prodotti/camden/</v>
       </c>
       <c r="Q27" t="str">
-        <v>sofas</v>
+        <v>divani</v>
       </c>
       <c r="R27" t="str">
         <v>TRUE</v>
@@ -1919,7 +1919,7 @@
         <v>Divano Camden</v>
       </c>
       <c r="C28" t="str">
-        <v>sofás</v>
+        <v>divani</v>
       </c>
       <c r="D28" t="str">
         <v>Camden unisce eleganza e comfort in un design armonioso e avvolgente. Personalizzabile nei rivestimenti, si adatta a spazi classici e moderni, offrendo stile, calore e funzionalità a ogni ambiente living.</v>
@@ -1931,7 +1931,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>divano, camden, sofás, sofa, sofá, couch, asiento, unisce, eleganza, comfort, design, armonioso, avvolgente, personalizzabile, rivestimenti, adatta, spazi, classici</v>
+        <v>divano, camden, divani, sofa, sofá, sofás, couch, asiento, unisce, eleganza, comfort, design, armonioso, avvolgente, personalizzabile, rivestimenti, adatta, spazi, classici</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1961,7 +1961,7 @@
         <v>https://www.febalcasa.com/it/prodotti/camden/</v>
       </c>
       <c r="Q28" t="str">
-        <v>sofas</v>
+        <v>divani</v>
       </c>
       <c r="R28" t="str">
         <v>TRUE</v>
@@ -1975,10 +1975,10 @@
         <v>Poltrone Astor</v>
       </c>
       <c r="C29" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="D29" t="str">
-        <v>Astor, la poltrona elegante e confortevole per arredare il soggiorno con stile. La poltrona Astor rappresenta una perfetta sintesi tra estetica e</v>
+        <v>La poltrona Astor rappresenta una perfetta sintesi tra estetica e funzionalità. Dotata di un'ampia seduta ergonomica e una struttura solida, offre il massimo del comfort per il relax quotidiano. La base girevole, disponibile in versione circolare o a raggiera, aggiunge praticità e movimento, rendendola ideale anche per ambienti dinamici. Il design pulito e contemporaneo la rende un complemento perfetto per soggiorni moderni o salotti raffinati. Astor è disponibile in una selezione di tessuti di alta qualità e tonalità neutre o vivaci, per adattarsi con eleganza a ogni stile d'arredo. Una poltrona confortevole, di design, progettata per chi desidera un ambiente accogliente e ricercato.</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1987,7 +1987,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>poltrone, astor, sillones, sillon, sillón, poltrona, armchair, elegante, confortevole, arredare, soggiorno, stile, rappresenta, perfetta, sintesi, estetica</v>
+        <v>poltrone, astor, sillon, sillón, sillones, poltrona, armchair, disponibile, design, rappresenta, perfetta, sintesi, estetica, funzionalita, dotata, ampia, seduta</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -2017,7 +2017,7 @@
         <v>https://www.febalcasa.com/it/prodotti/astor/</v>
       </c>
       <c r="Q29" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="R29" t="str">
         <v>TRUE</v>
@@ -2031,10 +2031,10 @@
         <v>Tavolini Ink</v>
       </c>
       <c r="C30" t="str">
-        <v>otros</v>
+        <v>altro</v>
       </c>
       <c r="D30" t="str">
-        <v>Elegante e funzionale, il coffee table Ink è adatto a qualsiasi stile. E' il complemento perfetto per accogliere una tazza di caffè durante una conversazione</v>
+        <v>Elegante e funzionale, il coffee table Ink è adatto a qualsiasi stile. E' il complemento perfetto per accogliere una tazza di caffè durante una conversazione o per esporre una selezione di oggetti preziosi in occasione di ospiti.</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -2043,7 +2043,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>tavolini, ink, otros, elegante, funzionale, coffee, table, adatto, qualsiasi, stile, complemento, perfetto, accogliere, tazza, caffe</v>
+        <v>tavolini, ink, altro, elegante, funzionale, coffee, table, adatto, qualsiasi, stile, complemento, perfetto, accogliere, tazza, caffe</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>https://www.febalcasa.com/it/prodotti/ink/</v>
       </c>
       <c r="Q30" t="str">
-        <v>otros</v>
+        <v>altro</v>
       </c>
       <c r="R30" t="str">
         <v>TRUE</v>
@@ -2087,7 +2087,7 @@
         <v>Cucina Origina Anta Libeskind022</v>
       </c>
       <c r="C31" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D31" t="str">
         <v>Cucina Origina Anta Libeskind022 — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>cucina, origina, anta, libeskind022, cocinas, cocina, kitchen, isla, casa, libeskind, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>cucina, origina, anta, libeskind022, cucine, cocina, cocinas, kitchen, isla, casa, libeskind, pieza, coleccion, febal, seccion, perfetta</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -2129,7 +2129,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-libeskind/</v>
       </c>
       <c r="Q31" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R31" t="str">
         <v>TRUE</v>
@@ -2143,7 +2143,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C32" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D32" t="str">
         <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
@@ -2155,7 +2155,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, casa, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, perfetta</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2185,7 +2185,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-libeskind/</v>
       </c>
       <c r="Q32" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R32" t="str">
         <v>TRUE</v>
@@ -2199,10 +2199,10 @@
         <v>Pouff Windsor</v>
       </c>
       <c r="C33" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="D33" t="str">
-        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento</v>
+        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento estremamente versatile che risponde a qualsiasi esigenza. La sua leggerezza permette di offrire soluzioni dinamiche per ogni stile di vita.</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -2211,7 +2211,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>pouff, windsor, puffs, puff, puf, ottoman, reposapies, pouf, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
+        <v>pouff, windsor, pouf, puff, puffs, puf, ottoman, reposapies, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -2241,7 +2241,7 @@
         <v>https://www.febalcasa.com/it/prodotti/windsor/</v>
       </c>
       <c r="Q33" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="R33" t="str">
         <v>TRUE</v>
@@ -2255,7 +2255,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C34" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D34" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -2267,7 +2267,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -2297,7 +2297,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q34" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R34" t="str">
         <v>TRUE</v>
@@ -2311,10 +2311,10 @@
         <v>Tavolo Phoenix</v>
       </c>
       <c r="C35" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="D35" t="str">
-        <v>Un’armonia di forme per il tavolo Phoenix, caratterizzato da un’imponente base geometrica e dal piano configurabile secondo il proprio stile. Il suggestivo</v>
+        <v>Un'armonia di forme per il tavolo Phoenix, caratterizzato da un'imponente base geometrica e dal piano configurabile secondo il proprio stile. Il suggestivo accostamento di materiali e finiture e l'equilibrio tra le proporzioni ne fanno un complemento di grande impatto estetico, in grado di donare prestigio a ogni ambiente. Il tavolo Phoenix è proposto con piani di varie dimensioni di forma rettangolare in variabile fissa o allungabile. I piani sono in Cristallo Lucido, Cristallo Velvet, Superceramica, Supermarmo Opaco, Supermarmo Lucido e Impiallacciato. La struttura è in metallo finitura Ottone scuro, Nero, Antracite o Sabbia.</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -2323,7 +2323,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>tavolo, phoenix, mesas, mesa, table, comedor, armonia, forme, caratterizzato, imponente, base, geometrica, piano, configurabile, secondo, proprio</v>
+        <v>tavolo, phoenix, tavoli, mesa, mesas, table, comedor, piani, cristallo, lucido, supermarmo, armonia, forme, caratterizzato, imponente, base, geometrica</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -2353,7 +2353,7 @@
         <v>https://www.febalcasa.com/it/prodotti/phoenix/</v>
       </c>
       <c r="Q35" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="R35" t="str">
         <v>TRUE</v>
@@ -2367,10 +2367,10 @@
         <v>Madia Libeskind022</v>
       </c>
       <c r="C36" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="D36" t="str">
-        <v>Il design è minimale e al contempo complesso: a seconda di come viene colpito dalla luce muta costantemente creando una superficie dinamica che si integra</v>
+        <v>Il design è minimale e al contempo complesso: a seconda di come viene colpito dalla luce muta costantemente creando una superficie dinamica che si integra allo stile di vita contemporaneo. Ad impreziosire il living e il dining, la madia LIBESKIND022 può essere configurata in 3 diverse tipologie: altezza H 75 cm in versione 3 ante o 4 ante e altezza H 154 cm in versione 2 ante. Oltre a poter essere configurata con ripiani interni in pannello o vetro e con un top laccato opaco o gres, la madia prevede la possibilità di inserire una cassettiera interna con maniglia integrata in legno per la versione H 75 cm e un kit allestimento bar per la versione H 154 cm con cassetto e un comodo piano estraibile.</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -2379,7 +2379,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>madia, libeskind022, aparadores, aparador, credenza, sideboard, buffet, design, minimale, contempo, complesso, seconda, viene, colpito, luce, muta, costantemente, creando, superficie</v>
+        <v>madia, libeskind022, madie, aparador, aparadores, credenza, sideboard, buffet, versione, ante, configurata, altezza, design, minimale, contempo, complesso, seconda, viene, colpito</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -2409,7 +2409,7 @@
         <v>https://www.febalcasa.com/it/prodotti/libeskind022/</v>
       </c>
       <c r="Q36" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="R36" t="str">
         <v>TRUE</v>
@@ -2423,10 +2423,10 @@
         <v>Poltrona Vivienne</v>
       </c>
       <c r="C37" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="D37" t="str">
-        <v>Poltrona Vivienne, il perfetto equilibrio tra design moderno e comfort avvolgente. La poltrona Vivienne è la scelta ideale per chi cerca un elemento d’arredo</v>
+        <v>La poltrona Vivienne è la scelta ideale per chi cerca un elemento d'arredo elegante e versatile per il soggiorno o la zona lettura. Il suo design raffinato e contemporaneo si distingue per linee morbide e proporzioni equilibrate, mentre la possibilità di scegliere tra base girevole a raggiera o circolare la rende funzionale e personalizzabile. Perfetta in contesti moderni o classici, Vivienne è realizzata con tessuti pregiati e finiture curate nei minimi dettagli. Una poltrona di design che coniuga estetica e benessere, pensata per completare con stile ogni ambiente living. Disponibile in diversi colori e rivestimenti, si adatta facilmente ad arredi contemporanei, diventando un'icona di comfort senza tempo.</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -2435,7 +2435,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>poltrona, vivienne, sillones, sillon, sillón, armchair, perfetto, equilibrio, design, moderno, comfort, avvolgente, scelta, ideale, cerca, elemento</v>
+        <v>poltrona, vivienne, poltrone, sillon, sillón, sillones, armchair, design, scelta, ideale, cerca, elemento, arredo, elegante, versatile, soggiorno, zona</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -2465,7 +2465,7 @@
         <v>https://www.febalcasa.com/it/prodotti/vivienne/</v>
       </c>
       <c r="Q37" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="R37" t="str">
         <v>TRUE</v>
@@ -2479,7 +2479,7 @@
         <v>Armadio Collezione Momenti.</v>
       </c>
       <c r="C38" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D38" t="str">
         <v>La lavanderia è l'ambiente della casa che richiede un occhio di riguardo, non solo dal punto di vista estetico, ma anche da quello pratico.</v>
@@ -2491,7 +2491,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>armadio, collezione, momenti., armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, lavanderia, ambiente, casa, richiede, occhio, riguardo, solo, punto, vista, estetico, quello, pratico</v>
+        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, lavanderia, ambiente, casa, richiede, occhio, riguardo, solo, punto, vista, estetico, quello, pratico</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -2521,7 +2521,7 @@
         <v>https://www.febalcasa.com/it/tipologia/mobili-di-servizi/mobili-di-servizi-laundry/</v>
       </c>
       <c r="Q38" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R38" t="str">
         <v>TRUE</v>
@@ -2535,10 +2535,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C39" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D39" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2577,7 +2577,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q39" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R39" t="str">
         <v>TRUE</v>
@@ -2591,7 +2591,7 @@
         <v>Letto Couple</v>
       </c>
       <c r="C40" t="str">
-        <v>dormitorio</v>
+        <v>camera da letto</v>
       </c>
       <c r="D40" t="str">
         <v>Letto Couple — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
@@ -2603,7 +2603,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>letto, couple, dormitorio, cama, bed, recamara, recámara, habitacion, gruppo notte, casa, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>letto, couple, camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, pieza, coleccion, febal, seccion, perfetta</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>dormitorio</v>
+        <v>camera-da-letto</v>
       </c>
       <c r="R40" t="str">
         <v>TRUE</v>
@@ -2647,10 +2647,10 @@
         <v>Poltrona Isabelle</v>
       </c>
       <c r="C41" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="D41" t="str">
-        <v>Isabelle, la poltroncina elegante e compatta per ambienti raffinati. Le poltroncine Isabelle sono la scelta ideale per chi desidera aggiungere un tocco di</v>
+        <v>Le poltroncine Isabelle sono la scelta ideale per chi desidera aggiungere un tocco di stile e comfort agli interni più curati. Compatte e raffinate, sono perfette per soggiorni eleganti, ingressi o angoli lettura. La loro forma armoniosa e i dettagli sartoriali valorizzano ogni ambiente, mentre i rivestimenti in tessuti di pregio ne esaltano il carattere ricercato. Isabelle si adatta facilmente a contesti moderni o classici, offrendo una soluzione versatile per chi cerca una poltroncina di design, comoda e dallo stile senza tempo. Disponibile in una gamma di finiture eleganti, è la poltroncina perfetta per completare il tuo arredamento con grazia e funzionalità.</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -2659,7 +2659,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>poltrona, isabelle, sillones, sillon, sillón, armchair, poltroncina, elegante, compatta, ambienti, raffinati, poltroncine, scelta, ideale, desidera, aggiungere, tocco</v>
+        <v>poltrona, isabelle, poltrone, sillon, sillón, sillones, armchair, stile, eleganti, poltroncina, poltroncine, scelta, ideale, desidera, aggiungere, tocco, comfort, interni</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -2689,7 +2689,7 @@
         <v>https://www.febalcasa.com/it/prodotti/isabelle/</v>
       </c>
       <c r="Q41" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="R41" t="str">
         <v>TRUE</v>
@@ -2703,10 +2703,10 @@
         <v>Specchio Polar</v>
       </c>
       <c r="C42" t="str">
-        <v>otros</v>
+        <v>altro</v>
       </c>
       <c r="D42" t="str">
-        <v>La specchiera Polar è progettata per essere posizionata a terra e offrire una visione completa della figura. Inoltre, può essere spostata agilmente e trovare</v>
+        <v>La specchiera Polar è progettata per essere posizionata a terra e offrire una visione completa della figura. Inoltre, può essere spostata agilmente e trovare posto in più ambienti della casa in base alle necessità del momento.</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2715,7 +2715,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>specchio, polar, otros, specchiera, progettata, posizionata, terra, offrire, visione, completa, figura, inoltre, spostata, agilmente</v>
+        <v>specchio, polar, altro, specchiera, progettata, posizionata, terra, offrire, visione, completa, figura, inoltre, spostata, agilmente</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -2745,7 +2745,7 @@
         <v>https://www.febalcasa.com/it/prodotti/polar/</v>
       </c>
       <c r="Q42" t="str">
-        <v>otros</v>
+        <v>altro</v>
       </c>
       <c r="R42" t="str">
         <v>TRUE</v>
@@ -2759,10 +2759,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C43" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D43" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q43" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R43" t="str">
         <v>TRUE</v>
@@ -2815,7 +2815,7 @@
         <v>Cabina Armadio Lapis</v>
       </c>
       <c r="C44" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D44" t="str">
         <v>Il sistema Lapis, configurabile a parete o a centro stanza, si integra perfettamente nella cabina armadio su misura e, grazie alla sua struttura, lascia filtrare la luce.</v>
@@ -2827,7 +2827,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>cabina, armadio, lapis, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, sistema, configurabile, parete, centro, stanza, integra, perfettamente, misura, grazie</v>
+        <v>cabina, armadio, lapis, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, sistema, configurabile, parete, centro, stanza, integra, perfettamente, misura, grazie</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -2857,7 +2857,7 @@
         <v>https://www.febalcasa.com/it/tipologia/cabine-armadio/lapis/</v>
       </c>
       <c r="Q44" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R44" t="str">
         <v>TRUE</v>
@@ -2871,10 +2871,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C45" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D45" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -2913,7 +2913,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q45" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R45" t="str">
         <v>TRUE</v>
@@ -2927,7 +2927,7 @@
         <v>Armadio Lewitt Plus</v>
       </c>
       <c r="C46" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D46" t="str">
         <v>L'armadio con anta battente Lewitt Plus con presa a gola continua unisce design e massima personalizzazione, ideale per ambienti contemporanei.</v>
@@ -2939,7 +2939,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>armadio, lewitt, plus, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, presa, gola, continua, unisce, design, massima, personalizzazione</v>
+        <v>armadio, lewitt, plus, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, presa, gola, continua, unisce, design, massima, personalizzazione</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -2969,7 +2969,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lewitt-plus/</v>
       </c>
       <c r="Q46" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R46" t="str">
         <v>TRUE</v>
@@ -2983,7 +2983,7 @@
         <v>Sistema Diciotto</v>
       </c>
       <c r="C47" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D47" t="str">
         <v>Diciotto è una parete attrezzata per la zona living di design: pratico, versatile e funzionale permette una modularità altissima.</v>
@@ -2995,7 +2995,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>sistema, diciotto, sistemas modulares, sistema modular, modular, parete, attrezzata, zona, living, design, pratico, versatile, funzionale, permette, modularita, altissima</v>
+        <v>sistema, diciotto, sistemi modulari, sistema modular, sistemas modulares, modular, parete, attrezzata, zona, living, design, pratico, versatile, funzionale, permette, modularita, altissima</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -3025,7 +3025,7 @@
         <v>https://www.febalcasa.com/it/prodotti/diciotto/</v>
       </c>
       <c r="Q47" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R47" t="str">
         <v>TRUE</v>
@@ -3039,7 +3039,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C48" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D48" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -3051,7 +3051,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -3081,7 +3081,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q48" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R48" t="str">
         <v>TRUE</v>
@@ -3095,7 +3095,7 @@
         <v>Divano Melrose</v>
       </c>
       <c r="C49" t="str">
-        <v>sofás</v>
+        <v>divani</v>
       </c>
       <c r="D49" t="str">
         <v>Melrose è un divano modulare dal design moderno e accogliente, pensato per unire stile, comfort e versatilità. Le linee morbide e i rivestimenti sartoriali lo rendono ideale per arredare con eleganza ogni spazio living contemporaneo.</v>
@@ -3107,7 +3107,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>divano, melrose, sofás, sofa, sofá, couch, asiento, modulare, design, moderno, accogliente, pensato, unire, stile, comfort, versatilita, linee</v>
+        <v>divano, melrose, divani, sofa, sofá, sofás, couch, asiento, modulare, design, moderno, accogliente, pensato, unire, stile, comfort, versatilita, linee</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>https://www.febalcasa.com/it/prodotti/melrose/</v>
       </c>
       <c r="Q49" t="str">
-        <v>sofas</v>
+        <v>divani</v>
       </c>
       <c r="R49" t="str">
         <v>TRUE</v>
@@ -3151,10 +3151,10 @@
         <v>Poltrona Andy</v>
       </c>
       <c r="C50" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="D50" t="str">
-        <v>Moderna e contemporanea, la nuova poltrona Andy presenta un design distintivo e allo stesso tempo confortevole per la vita di tutti i giorni. Le sue geometrie</v>
+        <v>Moderna e contemporanea, la nuova poltrona Andy presenta un design distintivo e allo stesso tempo confortevole per la vita di tutti i giorni. Le sue geometrie catturano l'attenzione e la rendono la protagonista dell'ambiente.</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -3163,7 +3163,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>poltrona, andy, sillones, sillon, sillón, armchair, moderna, contemporanea, nuova, presenta, design, distintivo, stesso, tempo, confortevole, vita</v>
+        <v>poltrona, andy, poltrone, sillon, sillón, sillones, armchair, moderna, contemporanea, nuova, presenta, design, distintivo, stesso, tempo, confortevole, vita</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -3193,7 +3193,7 @@
         <v>https://www.febalcasa.com/it/prodotti/andy/</v>
       </c>
       <c r="Q50" t="str">
-        <v>sillones</v>
+        <v>poltrone</v>
       </c>
       <c r="R50" t="str">
         <v>TRUE</v>
@@ -3207,7 +3207,7 @@
         <v>Gruppo Notte Marlene</v>
       </c>
       <c r="C51" t="str">
-        <v>dormitorio</v>
+        <v>camera da letto</v>
       </c>
       <c r="D51" t="str">
         <v>Marlene di Febal Casa: gruppo notte dalle forme curvilinee, disponibile con maniglia verticale in metallo e inserto in pelle. Top in gres e ampie opzioni di personalizzazione.</v>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>gruppo, notte, marlene, dormitorio, cama, letto, bed, recamara, recámara, habitacion, gruppo notte, febal, casa, forme, curvilinee, disponibile, maniglia, verticale, metallo, inserto</v>
+        <v>gruppo, notte, marlene, camera da letto, cama, dormitorio, letto, bed, recamara, recámara, habitacion, gruppo notte, febal, casa, forme, curvilinee, disponibile, maniglia, verticale, metallo, inserto</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -3249,7 +3249,7 @@
         <v>https://www.febalcasa.com/it/prodotti/febal-notte-gruppo-como-e-comodino-marlene/</v>
       </c>
       <c r="Q51" t="str">
-        <v>dormitorio</v>
+        <v>camera-da-letto</v>
       </c>
       <c r="R51" t="str">
         <v>TRUE</v>
@@ -3263,7 +3263,7 @@
         <v>Cucina Modula anta Square</v>
       </c>
       <c r="C52" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D52" t="str">
         <v>Cucina Modula anta Square — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3275,7 +3275,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>cucina, modula, anta, square, cocinas, cocina, kitchen, isla, casa, pieza, coleccion, febal, seccion, audace</v>
+        <v>cucina, modula, anta, square, cucine, cocina, cocinas, kitchen, isla, casa, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -3305,7 +3305,7 @@
         <v>https://www.febalcasa.com/it/prodotti/modula-anta-square/</v>
       </c>
       <c r="Q52" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R52" t="str">
         <v>TRUE</v>
@@ -3319,7 +3319,7 @@
         <v>Tavolo Madeira</v>
       </c>
       <c r="C53" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="D53" t="str">
         <v>Tavolo Madeira — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3331,7 +3331,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>tavolo, madeira, mesas, mesa, table, comedor, casa, pieza, coleccion, febal, seccion, audace</v>
+        <v>tavolo, madeira, tavoli, mesa, mesas, table, comedor, casa, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -3361,7 +3361,7 @@
         <v xml:space="preserve">https://www.febalcasa.com/it/prodotti/madeira/ </v>
       </c>
       <c r="Q53" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="R53" t="str">
         <v>TRUE</v>
@@ -3375,10 +3375,10 @@
         <v>Sedia Nina</v>
       </c>
       <c r="C54" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="D54" t="str">
-        <v>La sedia Nina può essere personalizzata con struttura in metallo oppure rivestita in abbinamento alla scocca. Il design è studiato per offrire una seduta</v>
+        <v>La sedia Nina può essere personalizzata con struttura in metallo oppure rivestita in abbinamento alla scocca. Il design è studiato per offrire una seduta confortevole e, se lo si desidera, aggiungere un tocco di colore alla zona dining.</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -3387,7 +3387,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>sedia, nina, sillas, silla, chair, asiento, personalizzata, struttura, metallo, oppure, rivestita, abbinamento, scocca, design, studiato, offrire</v>
+        <v>sedia, nina, sedie, silla, sillas, chair, asiento, personalizzata, struttura, metallo, oppure, rivestita, abbinamento, scocca, design, studiato, offrire</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -3417,7 +3417,7 @@
         <v>https://www.febalcasa.com/it/prodotti/nina/</v>
       </c>
       <c r="Q54" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="R54" t="str">
         <v>TRUE</v>
@@ -3431,7 +3431,7 @@
         <v>Madia Leaf</v>
       </c>
       <c r="C55" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="D55" t="str">
         <v>La madia Leaf, disponibile in due diverse altezze, si caratterizza per il suo disegno razionale impreziosito dalla maniglia incassata.</v>
@@ -3443,7 +3443,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>madia, leaf, aparadores, aparador, credenza, sideboard, buffet, disponibile, diverse, altezze, caratterizza, disegno, razionale, impreziosito, maniglia, incassata</v>
+        <v>madia, leaf, madie, aparador, aparadores, credenza, sideboard, buffet, disponibile, diverse, altezze, caratterizza, disegno, razionale, impreziosito, maniglia, incassata</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -3473,7 +3473,7 @@
         <v>https://www.febalcasa.com/it/prodotti/leaf/</v>
       </c>
       <c r="Q55" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="R55" t="str">
         <v>TRUE</v>
@@ -3487,7 +3487,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C56" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D56" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -3499,7 +3499,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -3529,7 +3529,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q56" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R56" t="str">
         <v>TRUE</v>
@@ -3543,7 +3543,7 @@
         <v>Gruppo Notte Marlene</v>
       </c>
       <c r="C57" t="str">
-        <v>dormitorio</v>
+        <v>camera da letto</v>
       </c>
       <c r="D57" t="str">
         <v>Astrid di Febal Casa: gruppo notte con vassoio superiore in cristallo e maniglie integrate nel disegno. Eleganza trasparente per la camera da letto contemporanea.</v>
@@ -3555,7 +3555,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>gruppo, notte, marlene, dormitorio, cama, letto, bed, recamara, recámara, habitacion, gruppo notte, astrid, febal, casa, vassoio, superiore, cristallo, maniglie, integrate, disegno, eleganza</v>
+        <v>gruppo, notte, marlene, camera da letto, cama, dormitorio, letto, bed, recamara, recámara, habitacion, gruppo notte, astrid, febal, casa, vassoio, superiore, cristallo, maniglie, integrate, disegno, eleganza</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -3585,7 +3585,7 @@
         <v>https://www.febalcasa.com/it/prodotti/astrid/</v>
       </c>
       <c r="Q57" t="str">
-        <v>dormitorio</v>
+        <v>camera-da-letto</v>
       </c>
       <c r="R57" t="str">
         <v>TRUE</v>
@@ -3599,10 +3599,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C58" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D58" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -3641,7 +3641,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q58" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R58" t="str">
         <v>TRUE</v>
@@ -3655,7 +3655,7 @@
         <v>Armadio Collezione Momenti.</v>
       </c>
       <c r="C59" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D59" t="str">
         <v>Armadio Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>armadio, collezione, momenti., armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -3697,7 +3697,7 @@
         <v>https://www.febalcasa.com/it/tipologia/momenti/cameretta/</v>
       </c>
       <c r="Q59" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R59" t="str">
         <v>TRUE</v>
@@ -3711,7 +3711,7 @@
         <v>Letto Collezione Momenti.</v>
       </c>
       <c r="C60" t="str">
-        <v>dormitorio</v>
+        <v>camera da letto</v>
       </c>
       <c r="D60" t="str">
         <v>Letto Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3723,7 +3723,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>letto, collezione, momenti., dormitorio, cama, bed, recamara, recámara, habitacion, gruppo notte, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>letto, collezione, momenti., camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -3753,7 +3753,7 @@
         <v>https://www.febalcasa.com/it/tipologia/momenti/cameretta/</v>
       </c>
       <c r="Q60" t="str">
-        <v>dormitorio</v>
+        <v>camera-da-letto</v>
       </c>
       <c r="R60" t="str">
         <v>TRUE</v>
@@ -3767,7 +3767,7 @@
         <v>Libreria Collezione Momenti.</v>
       </c>
       <c r="C61" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D61" t="str">
         <v>Libreria Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>libreria, collezione, momenti., librerías, librería, estanteria, estantería, bookshelf, estante, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>libreria, collezione, momenti., librerie, librería, librerías, estanteria, estantería, bookshelf, estante, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -3809,7 +3809,7 @@
         <v>https://www.febalcasa.com/it/tipologia/momenti/cameretta/</v>
       </c>
       <c r="Q61" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R61" t="str">
         <v>TRUE</v>
@@ -3823,10 +3823,10 @@
         <v>Pouff Windsor</v>
       </c>
       <c r="C62" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="D62" t="str">
-        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento</v>
+        <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento estremamente versatile che risponde a qualsiasi esigenza. La sua leggerezza permette di offrire soluzioni dinamiche per ogni stile di vita.</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -3835,7 +3835,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>pouff, windsor, puffs, puff, puf, ottoman, reposapies, pouf, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
+        <v>pouff, windsor, pouf, puff, puffs, puf, ottoman, reposapies, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.febalcasa.com/it/prodotti/windsor/</v>
       </c>
       <c r="Q62" t="str">
-        <v>puffs</v>
+        <v>pouf</v>
       </c>
       <c r="R62" t="str">
         <v>TRUE</v>
@@ -3879,7 +3879,7 @@
         <v>Armadio  Collezione Momenti.</v>
       </c>
       <c r="C63" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D63" t="str">
         <v>Armadio  Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
@@ -3891,7 +3891,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>armadio, collezione, momenti., armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -3921,7 +3921,7 @@
         <v>https://www.febalcasa.com/it/tipologia/momenti/cameretta/</v>
       </c>
       <c r="Q63" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R63" t="str">
         <v>TRUE</v>
@@ -3935,10 +3935,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C64" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D64" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -3977,7 +3977,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q64" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R64" t="str">
         <v>TRUE</v>
@@ -3991,7 +3991,7 @@
         <v>Libreria Trenta</v>
       </c>
       <c r="C65" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D65" t="str">
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
@@ -4003,7 +4003,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>libreria, trenta, librerías, librería, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
+        <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -4033,7 +4033,7 @@
         <v>https://www.febalcasa.com/it/prodotti/trenta/</v>
       </c>
       <c r="Q65" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R65" t="str">
         <v>TRUE</v>
@@ -4047,7 +4047,7 @@
         <v>Madia Onda - Zaha Hadid Architects</v>
       </c>
       <c r="C66" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="D66" t="str">
         <v>Madia Onda - Zaha Hadid Architects — pieza de la colección Febal Casa, sección CASA 04 - A-MARE.</v>
@@ -4059,7 +4059,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>madia, onda, zaha, hadid, architects, aparadores, aparador, credenza, sideboard, buffet, casa, pieza, coleccion, febal, seccion, mare</v>
+        <v>madia, onda, zaha, hadid, architects, madie, aparador, aparadores, credenza, sideboard, buffet, casa, pieza, coleccion, febal, seccion, mare</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -4089,7 +4089,7 @@
         <v>https://www.febalcasa.com/it/prodotti/madia-onda/</v>
       </c>
       <c r="Q66" t="str">
-        <v>aparadores</v>
+        <v>madie</v>
       </c>
       <c r="R66" t="str">
         <v>TRUE</v>
@@ -4103,7 +4103,7 @@
         <v>Divano Navigli</v>
       </c>
       <c r="C67" t="str">
-        <v>sofás</v>
+        <v>divani</v>
       </c>
       <c r="D67" t="str">
         <v>Disponibile in diverse tonalità e rivestimenti, il Divano Navigli è caratterizzato dall’ampiezza della seduta e dall’effetto trapuntatura continua.</v>
@@ -4115,7 +4115,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>divano, navigli, sofás, sofa, sofá, couch, asiento, dall, disponibile, diverse, tonalita, rivestimenti, caratterizzato, ampiezza, seduta, effetto, trapuntatura</v>
+        <v>divano, navigli, divani, sofa, sofá, sofás, couch, asiento, dall, disponibile, diverse, tonalita, rivestimenti, caratterizzato, ampiezza, seduta, effetto, trapuntatura</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -4145,7 +4145,7 @@
         <v>https://www.febalcasa.com/it/prodotti/navigli/</v>
       </c>
       <c r="Q67" t="str">
-        <v>sofas</v>
+        <v>divani</v>
       </c>
       <c r="R67" t="str">
         <v>TRUE</v>
@@ -4159,10 +4159,10 @@
         <v>Libreria Lapis</v>
       </c>
       <c r="C68" t="str">
-        <v>librerías</v>
+        <v>librerie</v>
       </c>
       <c r="D68" t="str">
-        <v>Il sistema libreria Lapis, configurabile a parete e centro stanza, si adatta perfettamente anche ad ambienti giorno e notte regalando estremo rigore e</v>
+        <v>Il sistema libreria Lapis, configurabile a parete e centro stanza, si adatta perfettamente anche ad ambienti giorno e notte regalando estremo rigore e contenimento. Il suo design inedito è personalizzabile grazie a diversi elementi compositivi: ripiani in vetro, in metallo o in pannello, pensili e basi in differenti modularità per soddisfare qualsiasi esigenza.</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -4171,7 +4171,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>libreria, lapis, librerías, librería, estanteria, estantería, bookshelf, estante, sistema, configurabile, parete, centro, stanza, adatta, perfettamente, ambienti, giorno, notte</v>
+        <v>libreria, lapis, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, sistema, configurabile, parete, centro, stanza, adatta, perfettamente, ambienti, giorno, notte</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lapis/</v>
       </c>
       <c r="Q68" t="str">
-        <v>librerias</v>
+        <v>librerie</v>
       </c>
       <c r="R68" t="str">
         <v>TRUE</v>
@@ -4215,7 +4215,7 @@
         <v>Sistema Origina</v>
       </c>
       <c r="C69" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D69" t="str">
         <v>Il design dell'anta sagoma37 è caratterizzato da una lavorazione inclinata a 37 gradi, scopri tutta la linea di mobili.</v>
@@ -4227,7 +4227,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>sistema, origina, sistemas modulares, sistema modular, modular, design, dell, anta, sagoma, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, design, dell, anta, sagoma, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -4257,7 +4257,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-sagoma37/</v>
       </c>
       <c r="Q69" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R69" t="str">
         <v>TRUE</v>
@@ -4271,7 +4271,7 @@
         <v>Cucina Origina Anta Sagoma 37</v>
       </c>
       <c r="C70" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D70" t="str">
         <v>Il design dell'anta sagoma37 è caratterizzato da una lavorazione inclinata a 37 gradi, scopri tutta la linea di mobili.</v>
@@ -4283,7 +4283,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>cucina, origina, anta, sagoma, cocinas, cocina, kitchen, isla, design, dell, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
+        <v>cucina, origina, anta, sagoma, cucine, cocina, cocinas, kitchen, isla, design, dell, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -4313,7 +4313,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-sagoma37/</v>
       </c>
       <c r="Q70" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R70" t="str">
         <v>TRUE</v>
@@ -4327,7 +4327,7 @@
         <v>Cucina Origina Anta Sagoma 37</v>
       </c>
       <c r="C71" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D71" t="str">
         <v>Il design dell'anta sagoma37 è caratterizzato da una lavorazione inclinata a 37 gradi, scopri tutta la linea di mobili.</v>
@@ -4339,7 +4339,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>cucina, origina, anta, sagoma, cocinas, cocina, kitchen, isla, design, dell, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
+        <v>cucina, origina, anta, sagoma, cucine, cocina, cocinas, kitchen, isla, design, dell, caratterizzato, lavorazione, inclinata, gradi, scopri, tutta, linea, mobili</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -4369,7 +4369,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-sagoma37/</v>
       </c>
       <c r="Q71" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R71" t="str">
         <v>TRUE</v>
@@ -4383,10 +4383,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C72" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D72" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -4395,7 +4395,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -4425,7 +4425,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q72" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R72" t="str">
         <v>TRUE</v>
@@ -4439,10 +4439,10 @@
         <v>Tavolo Leeds</v>
       </c>
       <c r="C73" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="D73" t="str">
-        <v>Il tavolo Leeds è disponibile in versione fissa e allungabile e in forma rettangolare o a botte per incontrare ogni esigenza di stile e spazio. La base</v>
+        <v>Il tavolo Leeds è disponibile in versione fissa e allungabile e in forma rettangolare o a botte per incontrare ogni esigenza di stile e spazio. La base scultorea è la caratteristica distintiva del modello: personalizzabile in cinque finiture metallo è in grado di abbinarsi perfettamente con i materiali del piano e dare vita a composizioni uniche.</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -4451,7 +4451,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>tavolo, leeds, mesas, mesa, table, comedor, disponibile, versione, fissa, allungabile, forma, rettangolare, botte, incontrare, ogni, esigenza</v>
+        <v>tavolo, leeds, tavoli, mesa, mesas, table, comedor, disponibile, versione, fissa, allungabile, forma, rettangolare, botte, incontrare, ogni, esigenza</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -4481,7 +4481,7 @@
         <v>https://www.febalcasa.com/it/prodotti/leeds/</v>
       </c>
       <c r="Q73" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="R73" t="str">
         <v>TRUE</v>
@@ -4495,10 +4495,10 @@
         <v>Sedia Nives con braccioli</v>
       </c>
       <c r="C74" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="D74" t="str">
-        <v>Eleganti e di design la sedia e la poltroncina Nives sono anche estremamente accoglienti grazie alla seduta imbottita e ai braccioli che assicurano avvolgenza</v>
+        <v>Eleganti e di design la sedia e la poltroncina Nives sono anche estremamente accoglienti grazie alla seduta imbottita e ai braccioli che assicurano avvolgenza e comodità. Le linee dolci e sinuose, la versatilità, l'ergonomia della seduta e dello schienale rendono Nives una vera e propria icona di comfort. L'alta qualità dei materiali, la cura sartoriale della realizzazione e i numerosi rivestimenti e finiture fanno di Nives l'elemento d'arredo giusto per conferire eleganza e forte personalità a qualsiasi ambiente. Le gambe sono personalizzabili in metallo verniciato nelle finiture Ottone scuro, Nero, Antracite e Sabbia per incontrare ogni esigenza.</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -4507,7 +4507,7 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>sedia, nives, braccioli, sillas, silla, chair, asiento, eleganti, design, poltroncina, estremamente, accoglienti, grazie, seduta, imbottita, assicurano</v>
+        <v>sedia, nives, braccioli, sedie, silla, sillas, chair, asiento, seduta, finiture, eleganti, design, poltroncina, estremamente, accoglienti, grazie, imbottita</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -4537,7 +4537,7 @@
         <v>https://www.febalcasa.com/it/prodotti/nives/</v>
       </c>
       <c r="Q74" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="R74" t="str">
         <v>TRUE</v>
@@ -4551,7 +4551,7 @@
         <v>Armadio Scorrevole Rodin</v>
       </c>
       <c r="C75" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D75" t="str">
         <v>L’armadio con anta scorrevole Rodin si distingue per la maniglia orizzontale con LED integrato, regolabile via app o telecomando.</v>
@@ -4563,7 +4563,7 @@
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>armadio, scorrevole, rodin, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, distingue, maniglia, orizzontale, integrato, regolabile, telecomando</v>
+        <v>armadio, scorrevole, rodin, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, distingue, maniglia, orizzontale, integrato, regolabile, telecomando</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -4593,7 +4593,7 @@
         <v>https://www.febalcasa.com/it/prodotti/rodin/</v>
       </c>
       <c r="Q75" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R75" t="str">
         <v>TRUE</v>
@@ -4607,7 +4607,7 @@
         <v>Cabina Armadio Hype</v>
       </c>
       <c r="C76" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D76" t="str">
         <v>Hype è un sistema modulare per cabine armadio con struttura a cremagliera, pensato per soluzioni lineari, angolari o su misura.</v>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>cabina, armadio, hype, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, sistema, modulare, cabine, struttura, cremagliera, pensato, soluzioni, lineari, angolari, misura</v>
+        <v>cabina, armadio, hype, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, sistema, modulare, cabine, struttura, cremagliera, pensato, soluzioni, lineari, angolari, misura</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -4649,7 +4649,7 @@
         <v>https://www.febalcasa.com/it/prodotti/hype/</v>
       </c>
       <c r="Q76" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R76" t="str">
         <v>TRUE</v>
@@ -4663,7 +4663,7 @@
         <v>Isola Onda - Zaha Hadid Architects</v>
       </c>
       <c r="C77" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D77" t="str">
         <v>Isola Onda - Zaha Hadid Architects — pieza de la colección Febal Casa, sección CASA 04 - A-MARE.</v>
@@ -4675,7 +4675,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>isola, onda, zaha, hadid, architects, cocinas, cocina, cucina, kitchen, isla, casa, pieza, coleccion, febal, seccion, mare</v>
+        <v>isola, onda, zaha, hadid, architects, cucine, cocina, cocinas, cucina, kitchen, isla, casa, pieza, coleccion, febal, seccion, mare</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -4705,7 +4705,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-isola-onda/</v>
       </c>
       <c r="Q77" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R77" t="str">
         <v>TRUE</v>
@@ -4719,7 +4719,7 @@
         <v>Sistema Origina anta Square</v>
       </c>
       <c r="C78" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D78" t="str">
         <v>L’anta square, disponibile con maniglia o con gola sagomata, integra perfettamente ambiente cucina e living creando spazi unici e multifunzionali.</v>
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>sistema, origina, anta, square, sistemas modulares, sistema modular, modular, disponibile, maniglia, gola, sagomata, integra, perfettamente, ambiente, cucina, living, creando</v>
+        <v>sistema, origina, anta, square, sistemi modulari, sistema modular, sistemas modulares, modular, disponibile, maniglia, gola, sagomata, integra, perfettamente, ambiente, cucina, living, creando</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -4761,7 +4761,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-square/</v>
       </c>
       <c r="Q78" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R78" t="str">
         <v>TRUE</v>
@@ -4775,7 +4775,7 @@
         <v>Sistema Origina anta Square</v>
       </c>
       <c r="C79" t="str">
-        <v>sistemas modulares</v>
+        <v>sistemi modulari</v>
       </c>
       <c r="D79" t="str">
         <v>L’anta square, disponibile con maniglia o con gola sagomata, integra perfettamente ambiente cucina e living creando spazi unici e multifunzionali.</v>
@@ -4787,7 +4787,7 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>sistema, origina, anta, square, sistemas modulares, sistema modular, modular, disponibile, maniglia, gola, sagomata, integra, perfettamente, ambiente, cucina, living, creando</v>
+        <v>sistema, origina, anta, square, sistemi modulari, sistema modular, sistemas modulares, modular, disponibile, maniglia, gola, sagomata, integra, perfettamente, ambiente, cucina, living, creando</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -4817,7 +4817,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-square/</v>
       </c>
       <c r="Q79" t="str">
-        <v>sistemas-modulares</v>
+        <v>sistemi-modulari</v>
       </c>
       <c r="R79" t="str">
         <v>TRUE</v>
@@ -4831,7 +4831,7 @@
         <v>Armadio Profile/ Leather</v>
       </c>
       <c r="C80" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D80" t="str">
         <v>L'armadio con anta battente Profile Leather di Febal Casa combina eleganza materica e funzionalità per un arredo raffinato.</v>
@@ -4843,7 +4843,7 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>armadio, profile/, leather, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, febal, casa, combina, eleganza, materica, funzionalita, arredo</v>
+        <v>armadio, profile/, leather, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, febal, casa, combina, eleganza, materica, funzionalita, arredo</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -4873,7 +4873,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-leather/</v>
       </c>
       <c r="Q80" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R80" t="str">
         <v>TRUE</v>
@@ -4887,7 +4887,7 @@
         <v>Armadio Profile/ Leather</v>
       </c>
       <c r="C81" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D81" t="str">
         <v>L'armadio con anta battente Profile Leather di Febal Casa combina eleganza materica e funzionalità per un arredo raffinato.</v>
@@ -4899,7 +4899,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>armadio, profile/, leather, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, febal, casa, combina, eleganza, materica, funzionalita, arredo</v>
+        <v>armadio, profile/, leather, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, febal, casa, combina, eleganza, materica, funzionalita, arredo</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-leather/</v>
       </c>
       <c r="Q81" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R81" t="str">
         <v>TRUE</v>
@@ -4943,7 +4943,7 @@
         <v>Armadio Profile/ Solid</v>
       </c>
       <c r="C82" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D82" t="str">
         <v>Solidità e design si incontrano nell’anta Profile Solid, per armadi battenti dal carattere moderno e di design.</v>
@@ -4955,7 +4955,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>armadio, profile/, solid, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, design, solidita, incontrano, nell, anta, profile, armadi, battenti, carattere, moderno</v>
+        <v>armadio, profile/, solid, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, design, solidita, incontrano, nell, anta, profile, battenti, carattere, moderno</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -4985,7 +4985,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-solid/</v>
       </c>
       <c r="Q82" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R82" t="str">
         <v>TRUE</v>
@@ -4999,7 +4999,7 @@
         <v>Armadio Profile/ Solid</v>
       </c>
       <c r="C83" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D83" t="str">
         <v>Solidità e design si incontrano nell’anta Profile Solid, per armadi battenti dal carattere moderno e di design.</v>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>armadio, profile/, solid, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, design, solidita, incontrano, nell, anta, profile, armadi, battenti, carattere, moderno</v>
+        <v>armadio, profile/, solid, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, design, solidita, incontrano, nell, anta, profile, battenti, carattere, moderno</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5041,7 +5041,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-solid/</v>
       </c>
       <c r="Q83" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R83" t="str">
         <v>TRUE</v>
@@ -5055,7 +5055,7 @@
         <v>Armadio Profile/ Reflex</v>
       </c>
       <c r="C84" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D84" t="str">
         <v>L'armadio con anta battente Profile Reflex riflette lo stile contemporaneo con finiture luminose e dettagli eleganti.</v>
@@ -5067,7 +5067,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>armadio, profile/, reflex, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, riflette, stile, contemporaneo, finiture, luminose, dettagli, eleganti</v>
+        <v>armadio, profile/, reflex, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, riflette, stile, contemporaneo, finiture, luminose, dettagli, eleganti</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -5097,7 +5097,7 @@
         <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-reflex/</v>
       </c>
       <c r="Q84" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R84" t="str">
         <v>TRUE</v>
@@ -5111,7 +5111,7 @@
         <v>Armadio battente Aurora</v>
       </c>
       <c r="C85" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D85" t="str">
         <v>L'armadio con anta battente Aurora è disegnata con un profilo a doppia cornice in metallo Carbon grey e può accogliere un vetro Ombra fumé o Stop-sol.</v>
@@ -5123,7 +5123,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>armadio, battente, aurora, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, disegnata, profilo, doppia, cornice, metallo, carbon, grey, accogliere</v>
+        <v>armadio, battente, aurora, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, disegnata, profilo, doppia, cornice, metallo, carbon, grey, accogliere</v>
       </c>
       <c r="H85" t="str">
         <v/>
@@ -5153,7 +5153,7 @@
         <v>https://www.febalcasa.com/it/prodotti/aurora-porta-battente/</v>
       </c>
       <c r="Q85" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R85" t="str">
         <v>TRUE</v>
@@ -5167,7 +5167,7 @@
         <v>Cucina Anta Telaio Alluminio vetro</v>
       </c>
       <c r="C86" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="D86" t="str">
         <v>L’anta con telaio in alluminio offre molteplici possibilità di personalizzazione grazie alle numerose finiture e possibilità di apertura.</v>
@@ -5179,7 +5179,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>cucina, anta, telaio, alluminio, vetro, cocinas, cocina, kitchen, isla, possibilita, offre, molteplici, personalizzazione, grazie, numerose, finiture, apertura</v>
+        <v>cucina, anta, telaio, alluminio, vetro, cucine, cocina, cocinas, kitchen, isla, possibilita, offre, molteplici, personalizzazione, grazie, numerose, finiture, apertura</v>
       </c>
       <c r="H86" t="str">
         <v/>
@@ -5209,7 +5209,7 @@
         <v>https://www.febalcasa.com/it/prodotti/origina-anta-telaio-alluminio/</v>
       </c>
       <c r="Q86" t="str">
-        <v>cocinas</v>
+        <v>cucine</v>
       </c>
       <c r="R86" t="str">
         <v>TRUE</v>
@@ -5223,7 +5223,7 @@
         <v>Armadio Barret</v>
       </c>
       <c r="C87" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D87" t="str">
         <v>L'armadio con anta battente Barret è contraddistinta da una piacevole essenzialità formale personalizzabile grazie alla gamma di maniglie dedicate.</v>
@@ -5235,7 +5235,7 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>armadio, barret, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, contraddistinta, piacevole, essenzialita, formale, personalizzabile, grazie, gamma, maniglie</v>
+        <v>armadio, barret, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, contraddistinta, piacevole, essenzialita, formale, personalizzabile, grazie, gamma, maniglie</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -5265,7 +5265,7 @@
         <v>https://www.febalcasa.com/it/prodotti/barret/</v>
       </c>
       <c r="Q87" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R87" t="str">
         <v>TRUE</v>
@@ -5279,10 +5279,10 @@
         <v>Sgabello Lola</v>
       </c>
       <c r="C88" t="str">
-        <v>taburetes</v>
+        <v>sgabelli</v>
       </c>
       <c r="D88" t="str">
-        <v>Disponibile con spalliera alta o bassa e in versione sgabello fisso o girevole, Lola presenta un design lineare ed estremo comfort. Accogliente e raffinata</v>
+        <v>Disponibile con spalliera alta o bassa e in versione sgabello fisso o girevole, Lola presenta un design lineare ed estremo comfort. Accogliente e raffinata Lola è adatta ad ogni contesto, anche il più sofisticato, grazie ai numerosi rivestimenti e alla forte ergonomia del modello. Lo schienale flessibile, offre una seduta estremamente comoda e piacevole che agevola l'appoggio della schiena assecondando il movimento del corpo. Le gambe sono disponibili in metallo verniciato nelle finiture Ottone scuro, nero, Antracite e Sabbia oppure rivestite in abbinamento alla seduta.</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>sgabello, lola, taburetes, taburete, banqueta, stool, bar, disponibile, spalliera, alta, bassa, versione, fisso, girevole, presenta, design, lineare</v>
+        <v>sgabello, lola, sgabelli, taburete, taburetes, banqueta, stool, bar, seduta, disponibile, spalliera, alta, bassa, versione, fisso, girevole, presenta, design</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5321,7 +5321,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lola/</v>
       </c>
       <c r="Q88" t="str">
-        <v>taburetes</v>
+        <v>sgabelli</v>
       </c>
       <c r="R88" t="str">
         <v>TRUE</v>
@@ -5335,7 +5335,7 @@
         <v>Armadio Lumia</v>
       </c>
       <c r="C89" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D89" t="str">
         <v>L'armadio con anta battente Lumia è un classico senza tempo nell'arredo della zona notte. Lumia presenta l’esclusiva illuminazione led integrata.</v>
@@ -5347,7 +5347,7 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>armadio, lumia, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, classico, senza, tempo, nell, arredo, zona, notte, presenta</v>
+        <v>armadio, lumia, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, classico, senza, tempo, nell, arredo, zona, notte, presenta</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5377,7 +5377,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lewitt-lumia/</v>
       </c>
       <c r="Q89" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R89" t="str">
         <v>TRUE</v>
@@ -5391,7 +5391,7 @@
         <v>Armadio Lumia</v>
       </c>
       <c r="C90" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D90" t="str">
         <v>L'armadio con anta battente Lumia è un classico senza tempo nell'arredo della zona notte. Lumia presenta l’esclusiva illuminazione led integrata.</v>
@@ -5403,7 +5403,7 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>armadio, lumia, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, classico, senza, tempo, nell, arredo, zona, notte, presenta</v>
+        <v>armadio, lumia, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, classico, senza, tempo, nell, arredo, zona, notte, presenta</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -5433,7 +5433,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lewitt-lumia/</v>
       </c>
       <c r="Q90" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R90" t="str">
         <v>TRUE</v>
@@ -5447,7 +5447,7 @@
         <v>Armadio Lewitt Plus</v>
       </c>
       <c r="C91" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="D91" t="str">
         <v>L'armadio con anta battente Lewitt Plus con presa a gola continua unisce design e massima personalizzazione, ideale per ambienti contemporanei.</v>
@@ -5459,7 +5459,7 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>armadio, lewitt, plus, armarios, armario, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, presa, gola, continua, unisce, design, massima, personalizzazione</v>
+        <v>armadio, lewitt, plus, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, presa, gola, continua, unisce, design, massima, personalizzazione</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
         <v>https://www.febalcasa.com/it/prodotti/lewitt-plus/</v>
       </c>
       <c r="Q91" t="str">
-        <v>armarios</v>
+        <v>armadi</v>
       </c>
       <c r="R91" t="str">
         <v>TRUE</v>
@@ -5503,10 +5503,10 @@
         <v>Tavolo Madeira</v>
       </c>
       <c r="C92" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="D92" t="str">
-        <v>L’armonioso intreccio di archi definisce un tavolo unico, protagonista di ogni ambiente. Le gambe inclinate e sovrapposte formano un disegno geometrico di</v>
+        <v>L'armonioso intreccio di archi definisce un tavolo unico, protagonista di ogni ambiente. Le gambe inclinate e sovrapposte formano un disegno geometrico di grande impatto visivo che gioca con la tridimensionalità ottenendo un risultato perfetto nato dall'eleganza, dall'equilibrio e dalla leggerezza dei volumi. La base in metallo è disponibile in finitura Ottone Scuro, Nero, Antracite e Sabbia. Il piano è di forma rotonda, ovale fisso o allungabile ed è configurabile in Cristallo Lucido, Cristallo Velvet, Superceramica, Supermarmo opaco, Supermarmo lucido e legno Impiallacciato. La versione fissa può essere arricchita con il piano centrotavola girevole, un dispositivo rotante che permette di condividere facilmente cibi e oggetti con tutti i commensali.</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -5515,7 +5515,7 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>tavolo, madeira, mesas, mesa, table, comedor, armonioso, intreccio, archi, definisce, unico, protagonista, ogni, ambiente, gambe, inclinate, sovrapposte</v>
+        <v>tavolo, madeira, tavoli, mesa, mesas, table, comedor, dall, piano, cristallo, lucido, supermarmo, armonioso, intreccio, archi, definisce, unico, protagonista</v>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -5545,7 +5545,7 @@
         <v>https://www.febalcasa.com/it/prodotti/madeira/</v>
       </c>
       <c r="Q92" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="R92" t="str">
         <v>TRUE</v>
@@ -5559,10 +5559,10 @@
         <v>Sedia Dea</v>
       </c>
       <c r="C93" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="D93" t="str">
-        <v>La sedia Dea è perfetta per progetti raffinati in ogni dettaglio. La linearità delle gambe in metallo verniciato disponibile nelle finiture Ottone scuro,</v>
+        <v>La sedia Dea è perfetta per progetti raffinati in ogni dettaglio. La linearità delle gambe in metallo verniciato disponibile nelle finiture Ottone scuro, Antracite, Nero e Sabbia è ammorbidita dalle forme curve e accoglienti della seduta e dello schienale, arricchite da un prezioso tocco sartoriale che si rivela con il grazioso movimento di pieghe che enfatizza i volumi e il senso di comfort. Dea è una sedia di valore che cattura inevitabilmente l'ammirazione di chiunque la osservi.</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -5571,7 +5571,7 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>sedia, dea, sillas, silla, chair, asiento, perfetta, progetti, raffinati, ogni, dettaglio, linearita, gambe, metallo, verniciato, disponibile, nelle</v>
+        <v>sedia, dea, sedie, silla, sillas, chair, asiento, perfetta, progetti, raffinati, ogni, dettaglio, linearita, gambe, metallo, verniciato, disponibile, nelle</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5601,7 +5601,7 @@
         <v>https://www.febalcasa.com/it/prodotti/dea/</v>
       </c>
       <c r="Q93" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="R93" t="str">
         <v>TRUE</v>
@@ -5615,10 +5615,10 @@
         <v>Tavolo Daniel</v>
       </c>
       <c r="C94" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="D94" t="str">
-        <v>Sinonimo di estrema eleganza, il tavolo Daniel con struttura ponte gamba rappresenta il punto centrale della sala da pranzo, il luogo dove si riuniscono</v>
+        <v>Sinonimo di estrema eleganza, il tavolo Daniel con struttura ponte gamba rappresenta il punto centrale della sala da pranzo, il luogo dove si riuniscono familiari e amici. Il suo piano personalizzabile in cristallo, superceramica e supermarmo accoglie comodamente i commensali garantendo qualità negli anni. Il modello è disponibile in forma quadrata, rettangolare e rettangolare allungabile.</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -5627,7 +5627,7 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>tavolo, daniel, mesas, mesa, table, comedor, sinonimo, estrema, eleganza, struttura, ponte, gamba, rappresenta, punto, centrale, sala</v>
+        <v>tavolo, daniel, tavoli, mesa, mesas, table, comedor, rettangolare, sinonimo, estrema, eleganza, struttura, ponte, gamba, rappresenta, punto, centrale</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5657,7 +5657,7 @@
         <v>https://www.febalcasa.com/it/prodotti/daniel/</v>
       </c>
       <c r="Q94" t="str">
-        <v>mesas</v>
+        <v>tavoli</v>
       </c>
       <c r="R94" t="str">
         <v>TRUE</v>
@@ -5671,10 +5671,10 @@
         <v>Sedia Dea</v>
       </c>
       <c r="C95" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="D95" t="str">
-        <v>La sedia Dea è perfetta per progetti raffinati in ogni dettaglio. La linearità delle gambe in metallo verniciato disponibile nelle finiture Ottone scuro,</v>
+        <v>La sedia Dea è perfetta per progetti raffinati in ogni dettaglio. La linearità delle gambe in metallo verniciato disponibile nelle finiture Ottone scuro, Antracite, Nero e Sabbia è ammorbidita dalle forme curve e accoglienti della seduta e dello schienale, arricchite da un prezioso tocco sartoriale che si rivela con il grazioso movimento di pieghe che enfatizza i volumi e il senso di comfort. Dea è una sedia di valore che cattura inevitabilmente l'ammirazione di chiunque la osservi.</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -5683,7 +5683,7 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>sedia, dea, sillas, silla, chair, asiento, perfetta, progetti, raffinati, ogni, dettaglio, linearita, gambe, metallo, verniciato, disponibile, nelle</v>
+        <v>sedia, dea, sedie, silla, sillas, chair, asiento, perfetta, progetti, raffinati, ogni, dettaglio, linearita, gambe, metallo, verniciato, disponibile, nelle</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -5713,7 +5713,7 @@
         <v>https://www.febalcasa.com/it/prodotti/dea/</v>
       </c>
       <c r="Q95" t="str">
-        <v>sillas</v>
+        <v>sedie</v>
       </c>
       <c r="R95" t="str">
         <v>TRUE</v>
@@ -5727,10 +5727,10 @@
         <v>Boiserie</v>
       </c>
       <c r="C96" t="str">
-        <v>paneles decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="D96" t="str">
-        <v>La parete attrezzata boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa</v>
+        <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -5739,7 +5739,7 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>boiserie, paneles decorativos, panel, revestimiento, pared, decorativo, columna, vertical, parete, attrezzata, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal</v>
+        <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -5769,7 +5769,7 @@
         <v>https://www.febalcasa.com/it/prodotti/boiserie/</v>
       </c>
       <c r="Q96" t="str">
-        <v>paneles-decorativos</v>
+        <v>boiserie</v>
       </c>
       <c r="R96" t="str">
         <v>TRUE</v>

--- a/clients/febal-casa/catalog.xlsx
+++ b/clients/febal-casa/catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:T96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,6 +454,12 @@
       <c r="R1" t="str">
         <v>active</v>
       </c>
+      <c r="S1" t="str">
+        <v>shape</v>
+      </c>
+      <c r="T1" t="str">
+        <v>style</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -510,6 +516,12 @@
       <c r="R2" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -566,6 +578,12 @@
       <c r="R3" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -622,6 +640,12 @@
       <c r="R4" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S4" t="str">
+        <v>ad angolo</v>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -678,6 +702,12 @@
       <c r="R5" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -734,6 +764,12 @@
       <c r="R6" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -790,6 +826,12 @@
       <c r="R7" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -846,6 +888,12 @@
       <c r="R8" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -902,6 +950,12 @@
       <c r="R9" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -958,6 +1012,12 @@
       <c r="R10" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1014,6 +1074,12 @@
       <c r="R11" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1070,6 +1136,12 @@
       <c r="R12" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1126,6 +1198,12 @@
       <c r="R13" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1182,6 +1260,12 @@
       <c r="R14" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1238,6 +1322,12 @@
       <c r="R15" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1294,6 +1384,12 @@
       <c r="R16" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1350,6 +1446,12 @@
       <c r="R17" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1406,6 +1508,12 @@
       <c r="R18" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1462,6 +1570,12 @@
       <c r="R19" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1518,6 +1632,12 @@
       <c r="R20" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1574,6 +1694,12 @@
       <c r="R21" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1630,6 +1756,12 @@
       <c r="R22" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1686,6 +1818,12 @@
       <c r="R23" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1742,6 +1880,12 @@
       <c r="R24" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1798,6 +1942,12 @@
       <c r="R25" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1854,6 +2004,12 @@
       <c r="R26" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1910,6 +2066,12 @@
       <c r="R27" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1966,6 +2128,12 @@
       <c r="R28" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -2022,6 +2190,12 @@
       <c r="R29" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -2078,6 +2252,12 @@
       <c r="R30" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -2134,6 +2314,12 @@
       <c r="R31" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -2190,6 +2376,12 @@
       <c r="R32" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -2246,6 +2438,12 @@
       <c r="R33" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2302,6 +2500,12 @@
       <c r="R34" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2358,6 +2562,12 @@
       <c r="R35" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2414,6 +2624,12 @@
       <c r="R36" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2470,6 +2686,12 @@
       <c r="R37" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2526,6 +2748,12 @@
       <c r="R38" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2582,6 +2810,12 @@
       <c r="R39" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2638,6 +2872,12 @@
       <c r="R40" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2694,6 +2934,12 @@
       <c r="R41" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2750,6 +2996,12 @@
       <c r="R42" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
+      <c r="T42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2806,6 +3058,12 @@
       <c r="R43" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2862,6 +3120,12 @@
       <c r="R44" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
+      <c r="T44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2918,6 +3182,12 @@
       <c r="R45" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
+      <c r="T45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2974,6 +3244,12 @@
       <c r="R46" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
+      <c r="T46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -3030,6 +3306,12 @@
       <c r="R47" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S47" t="str">
+        <v/>
+      </c>
+      <c r="T47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -3086,6 +3368,12 @@
       <c r="R48" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S48" t="str">
+        <v/>
+      </c>
+      <c r="T48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -3142,6 +3430,12 @@
       <c r="R49" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S49" t="str">
+        <v>ad angolo</v>
+      </c>
+      <c r="T49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3198,6 +3492,12 @@
       <c r="R50" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S50" t="str">
+        <v/>
+      </c>
+      <c r="T50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -3254,6 +3554,12 @@
       <c r="R51" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S51" t="str">
+        <v/>
+      </c>
+      <c r="T51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3310,6 +3616,12 @@
       <c r="R52" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S52" t="str">
+        <v/>
+      </c>
+      <c r="T52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3366,6 +3678,12 @@
       <c r="R53" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
+      <c r="T53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3422,6 +3740,12 @@
       <c r="R54" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3478,6 +3802,12 @@
       <c r="R55" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3534,6 +3864,12 @@
       <c r="R56" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S56" t="str">
+        <v/>
+      </c>
+      <c r="T56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3590,6 +3926,12 @@
       <c r="R57" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S57" t="str">
+        <v/>
+      </c>
+      <c r="T57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3646,6 +3988,12 @@
       <c r="R58" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
+      <c r="T58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3702,6 +4050,12 @@
       <c r="R59" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+      <c r="T59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3758,6 +4112,12 @@
       <c r="R60" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3814,6 +4174,12 @@
       <c r="R61" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3870,6 +4236,12 @@
       <c r="R62" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3926,6 +4298,12 @@
       <c r="R63" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+      <c r="T63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3982,6 +4360,12 @@
       <c r="R64" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+      <c r="T64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -4038,6 +4422,12 @@
       <c r="R65" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -4094,6 +4484,12 @@
       <c r="R66" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+      <c r="T66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -4150,6 +4546,12 @@
       <c r="R67" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -4206,6 +4608,12 @@
       <c r="R68" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -4262,6 +4670,12 @@
       <c r="R69" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -4318,6 +4732,12 @@
       <c r="R70" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -4374,6 +4794,12 @@
       <c r="R71" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -4430,6 +4856,12 @@
       <c r="R72" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4486,6 +4918,12 @@
       <c r="R73" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4542,6 +4980,12 @@
       <c r="R74" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4598,6 +5042,12 @@
       <c r="R75" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4654,6 +5104,12 @@
       <c r="R76" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4710,6 +5166,12 @@
       <c r="R77" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4766,6 +5228,12 @@
       <c r="R78" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4822,6 +5290,12 @@
       <c r="R79" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4878,6 +5352,12 @@
       <c r="R80" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4934,6 +5414,12 @@
       <c r="R81" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4990,6 +5476,12 @@
       <c r="R82" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -5046,6 +5538,12 @@
       <c r="R83" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -5102,6 +5600,12 @@
       <c r="R84" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -5158,6 +5662,12 @@
       <c r="R85" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -5214,6 +5724,12 @@
       <c r="R86" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -5270,6 +5786,12 @@
       <c r="R87" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -5326,6 +5848,12 @@
       <c r="R88" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -5382,6 +5910,12 @@
       <c r="R89" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -5438,6 +5972,12 @@
       <c r="R90" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -5494,6 +6034,12 @@
       <c r="R91" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -5550,6 +6096,12 @@
       <c r="R92" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -5606,6 +6158,12 @@
       <c r="R93" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -5662,6 +6220,12 @@
       <c r="R94" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -5718,6 +6282,12 @@
       <c r="R95" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5774,10 +6344,16 @@
       <c r="R96" t="str">
         <v>TRUE</v>
       </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/clients/febal-casa/catalog.xlsx
+++ b/clients/febal-casa/catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:U102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,10 +460,13 @@
       <c r="T1" t="str">
         <v>style</v>
       </c>
+      <c r="U1" t="str">
+        <v>finish</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>box-100-b-103-boiserie-camino</v>
+        <v>FEB-001</v>
       </c>
       <c r="B2" t="str">
         <v>Boiserie camino</v>
@@ -475,10 +478,10 @@
         <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>nero/grigio scuro venato</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>pannello effetto pietra</v>
       </c>
       <c r="G2" t="str">
         <v>boiserie, camino, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
@@ -490,16 +493,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J2" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>-81</v>
+        <v>-56.4</v>
       </c>
       <c r="L2">
-        <v>-4</v>
+        <v>-29.5</v>
       </c>
       <c r="M2">
-        <v>70</v>
+        <v>111.2</v>
       </c>
       <c r="N2" t="str">
         <v>BOX 100 - B_103</v>
@@ -517,15 +520,18 @@
         <v>TRUE</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>boiserie modulare a tutta altezza</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Scenario</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>box-100-b-104-boiserie</v>
+        <v>FEB-002</v>
       </c>
       <c r="B3" t="str">
         <v>Boiserie</v>
@@ -537,10 +543,10 @@
         <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>tortora/beige</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>pannello laccato</v>
       </c>
       <c r="G3" t="str">
         <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
@@ -555,13 +561,13 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>46</v>
+        <v>39.6</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="M3">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="N3" t="str">
         <v>BOX 100 - B_104</v>
@@ -579,15 +585,18 @@
         <v>TRUE</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>boiserie modulare a tutta altezza</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>box-100-b-106-divano-balmoral</v>
+        <v>FEB-003</v>
       </c>
       <c r="B4" t="str">
         <v>Divano Balmoral</v>
@@ -599,10 +608,10 @@
         <v>Un divano componibile pensato per interpretare le esigenze abitative contemporanee, coniugando estetica, ergonomia e versatilità. La scelta ideale per un soggiorno elegante, accogliente e su misura.</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>verde oliva</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>tessuto</v>
       </c>
       <c r="G4" t="str">
         <v>divano, balmoral, divani, sofa, sofá, sofás, couch, asiento, componibile, pensato, interpretare, esigenze, abitative, contemporanee, coniugando, estetica, ergonomia, versatilita, scelta</v>
@@ -617,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="K4">
-        <v>-135</v>
+        <v>-152.7</v>
       </c>
       <c r="L4">
-        <v>-48</v>
+        <v>-52.8</v>
       </c>
       <c r="M4">
-        <v>70</v>
+        <v>101.4</v>
       </c>
       <c r="N4" t="str">
         <v>BOX 100 - B_106</v>
@@ -644,12 +653,15 @@
         <v>ad angolo</v>
       </c>
       <c r="T4" t="str">
+        <v>Contemporaneo, Classico elegante</v>
+      </c>
+      <c r="U4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>box-100-b-109-tavolino-rio</v>
+        <v>FEB-004</v>
       </c>
       <c r="B5" t="str">
         <v>Tavolino Rio</v>
@@ -661,10 +673,10 @@
         <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>marrone scuro/nero venato</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>marmo</v>
       </c>
       <c r="G5" t="str">
         <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
@@ -679,13 +691,13 @@
         <v>11</v>
       </c>
       <c r="K5">
-        <v>89</v>
+        <v>98.1</v>
       </c>
       <c r="L5">
-        <v>-48</v>
+        <v>-50</v>
       </c>
       <c r="M5">
-        <v>70</v>
+        <v>75.8</v>
       </c>
       <c r="N5" t="str">
         <v>BOX 100 - B_109</v>
@@ -706,12 +718,15 @@
         <v/>
       </c>
       <c r="T5" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>box-100-b-110-tavolino-rio</v>
+        <v>FEB-005</v>
       </c>
       <c r="B6" t="str">
         <v>Tavolino Rio</v>
@@ -723,10 +738,10 @@
         <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>legno naturale</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>legno</v>
       </c>
       <c r="G6" t="str">
         <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
@@ -738,16 +753,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J6" t="str">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-44</v>
+        <v>95.3</v>
       </c>
       <c r="L6">
-        <v>-22</v>
+        <v>-38.5</v>
       </c>
       <c r="M6">
-        <v>70</v>
+        <v>93.9</v>
       </c>
       <c r="N6" t="str">
         <v>BOX 100 - B_110</v>
@@ -768,12 +783,15 @@
         <v/>
       </c>
       <c r="T6" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>box-100-b-125-boiserie</v>
+        <v>FEB-006</v>
       </c>
       <c r="B7" t="str">
         <v>Boiserie</v>
@@ -785,10 +803,10 @@
         <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>nero venato bianco</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>pannello effetto pietra</v>
       </c>
       <c r="G7" t="str">
         <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
@@ -800,16 +818,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J7" t="str">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>-63</v>
+        <v>35.7</v>
       </c>
       <c r="L7">
-        <v>-18</v>
+        <v>6.1</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N7" t="str">
         <v>BOX 100 - B_125</v>
@@ -827,15 +845,18 @@
         <v>TRUE</v>
       </c>
       <c r="S7" t="str">
-        <v/>
+        <v>boiserie modulare a tutta altezza</v>
       </c>
       <c r="T7" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Scenario</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>box-120-b-121-cucina-origina-anta-square-cannettato</v>
+        <v>FEB-007</v>
       </c>
       <c r="B8" t="str">
         <v>Cucina Origina Anta Square Cannettato</v>
@@ -844,16 +865,16 @@
         <v>cucine</v>
       </c>
       <c r="D8" t="str">
-        <v>Cucina Origina Anta Square Cannettato — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
+        <v>Cucina Origina Anta Square Cannettato — elemento della collezione Febal Casa, sezione CASA 01 - AUTENTICA.</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>rovere biondo, marmo marrone scuro venato</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>legno, marmo</v>
       </c>
       <c r="G8" t="str">
-        <v>cucina, origina, anta, square, cannettato, cucine, cocina, cocinas, kitchen, isla, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>cucina, origina, anta, square, cannettato, cucine, cocina, cocinas, kitchen, isla, casa, elemento, collezione, febal, sezione, autentica</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -862,16 +883,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J8" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-6</v>
+        <v>52.7</v>
       </c>
       <c r="L8">
-        <v>-17</v>
+        <v>-36.9</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="N8" t="str">
         <v>BOX 120 - B_121</v>
@@ -889,15 +910,18 @@
         <v>TRUE</v>
       </c>
       <c r="S8" t="str">
-        <v/>
+        <v>cucina componibile a isola</v>
       </c>
       <c r="T8" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Impiallacciato Opaco Cannettato</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>box-120-b-122-sistema-origina</v>
+        <v>FEB-008</v>
       </c>
       <c r="B9" t="str">
         <v>Sistema Origina</v>
@@ -906,16 +930,16 @@
         <v>sistemi modulari</v>
       </c>
       <c r="D9" t="str">
-        <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
+        <v>Sistema Origina — elemento della collezione Febal Casa, sezione CASA 01 - AUTENTICA.</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>rovere biondo, marmo marrone scuro venato</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>legno, marmo</v>
       </c>
       <c r="G9" t="str">
-        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, elemento, collezione, febal, sezione, autentica</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -924,16 +948,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J9" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="L9">
-        <v>-5</v>
+        <v>-3.4</v>
       </c>
       <c r="M9">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N9" t="str">
         <v>BOX 120 - B_122</v>
@@ -954,12 +978,15 @@
         <v/>
       </c>
       <c r="T9" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Impiallacciato Opaco Cannettato</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>box-120-b-123-sistema-origina</v>
+        <v>FEB-009</v>
       </c>
       <c r="B10" t="str">
         <v>Sistema Origina</v>
@@ -968,16 +995,16 @@
         <v>sistemi modulari</v>
       </c>
       <c r="D10" t="str">
-        <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 01 - AUTENTICA.</v>
+        <v>Sistema Origina — elemento della collezione Febal Casa, sezione CASA 01 - AUTENTICA.</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>rovere biondo, marmo marrone scuro venato</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>legno, marmo</v>
       </c>
       <c r="G10" t="str">
-        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, autentica</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, elemento, collezione, febal, sezione, autentica</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -989,13 +1016,13 @@
         <v>2</v>
       </c>
       <c r="K10">
-        <v>-7</v>
+        <v>136</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>-5.8</v>
       </c>
       <c r="M10">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N10" t="str">
         <v>BOX 120 - B_123</v>
@@ -1016,12 +1043,15 @@
         <v/>
       </c>
       <c r="T10" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Impiallacciato Opaco Cannettato</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>box-140-b-141-sistema-diciotto</v>
+        <v>FEB-010</v>
       </c>
       <c r="B11" t="str">
         <v>Sistema Diciotto</v>
@@ -1033,10 +1063,10 @@
         <v>Diciotto è una parete attrezzata per la zona living di design: pratico, versatile e funzionale permette una modularità altissima.</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>antracite</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>pannello laccato</v>
       </c>
       <c r="G11" t="str">
         <v>sistema, diciotto, sistemi modulari, sistema modular, sistemas modulares, modular, parete, attrezzata, zona, living, design, pratico, versatile, funzionale, permette, modularita, altissima</v>
@@ -1051,13 +1081,13 @@
         <v>19</v>
       </c>
       <c r="K11">
-        <v>-91</v>
+        <v>13.8</v>
       </c>
       <c r="L11">
-        <v>-3</v>
+        <v>-0.4</v>
       </c>
       <c r="M11">
-        <v>70</v>
+        <v>70.6</v>
       </c>
       <c r="N11" t="str">
         <v>BOX 140 - B_141</v>
@@ -1075,15 +1105,18 @@
         <v>TRUE</v>
       </c>
       <c r="S11" t="str">
-        <v/>
+        <v>parete attrezzata modulare</v>
       </c>
       <c r="T11" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>box-140-b-142-libreria-trenta</v>
+        <v>FEB-011</v>
       </c>
       <c r="B12" t="str">
         <v>Libreria Trenta</v>
@@ -1095,10 +1128,10 @@
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>antracite</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>pannello laccato, vetro</v>
       </c>
       <c r="G12" t="str">
         <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
@@ -1134,18 +1167,21 @@
         <v>librerie</v>
       </c>
       <c r="R12" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>libreria modulare</v>
       </c>
       <c r="T12" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U12" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>box-140-b-143-libreria-trenta</v>
+        <v>FEB-012</v>
       </c>
       <c r="B13" t="str">
         <v>Libreria Trenta</v>
@@ -1157,10 +1193,10 @@
         <v>Trenta è la libreria interpretata da Febal Casa come elemento chiave intorno cui viene progettata la zona giorno.</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>antracite</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>pannello laccato, vetro</v>
       </c>
       <c r="G13" t="str">
         <v>libreria, trenta, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, interpretata, febal, casa, elemento, chiave, intorno, viene, progettata, zona, giorno</v>
@@ -1172,16 +1208,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J13" t="str">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K13">
-        <v>22</v>
+        <v>149.6</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M13">
-        <v>70</v>
+        <v>105.2</v>
       </c>
       <c r="N13" t="str">
         <v>BOX 140 - B_143</v>
@@ -1199,15 +1235,18 @@
         <v>TRUE</v>
       </c>
       <c r="S13" t="str">
-        <v/>
+        <v>libreria modulare</v>
       </c>
       <c r="T13" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U13" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>box-140-b-146-madie-aurora</v>
+        <v>FEB-013</v>
       </c>
       <c r="B14" t="str">
         <v>Madie Aurora</v>
@@ -1219,10 +1258,10 @@
         <v>La madia Aurora si distingue per la leggerezza dei volumi e l’estetica ricercata. Arreda la tua Casa con Febal Casa.</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>noce, carbon grey</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>legno, metallo, vetro</v>
       </c>
       <c r="G14" t="str">
         <v>madie, aurora, aparador, aparadores, madia, credenza, sideboard, buffet, casa, distingue, leggerezza, volumi, estetica, ricercata, arreda, febal</v>
@@ -1234,16 +1273,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J14" t="str">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K14">
-        <v>-173</v>
+        <v>76.5</v>
       </c>
       <c r="L14">
-        <v>-31</v>
+        <v>-14.4</v>
       </c>
       <c r="M14">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N14" t="str">
         <v>BOX 140 - B_146</v>
@@ -1264,12 +1303,15 @@
         <v/>
       </c>
       <c r="T14" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>box-140-b-148-tavolino-rio</v>
+        <v>FEB-014</v>
       </c>
       <c r="B15" t="str">
         <v>Tavolino Rio</v>
@@ -1281,10 +1323,10 @@
         <v>Il tavolino Rio è contraddistinto da una struttura in metallo che presenta la particolarità di poter accogliere riviste e giornali. Una funzione che lo rende il compagno ideale nei momenti di relax. Il piano può essere configurato a seconda del proprio gusto in finitura laccata opaca o impiallacciata.</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>marrone scuro/nero venato</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>marmo</v>
       </c>
       <c r="G15" t="str">
         <v>tavolino, rio, tavolini, mesa de centro, mesita, coffee table, contraddistinto, struttura, metallo, presenta, particolarita, poter, accogliere, riviste, giornali, funzione, rende</v>
@@ -1320,18 +1362,21 @@
         <v>tavolini</v>
       </c>
       <c r="R15" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S15" t="str">
         <v/>
       </c>
       <c r="T15" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>box-160-b-161-armadio-profile-block</v>
+        <v>FEB-015</v>
       </c>
       <c r="B16" t="str">
         <v>Armadio Profile/ Block</v>
@@ -1343,10 +1388,10 @@
         <v>L'armadio con anta battente Profile Block si distingue per le sue linee nette e moderne, perfetta per un armadio dal carattere deciso.</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>bronzo/champagne metallizzato</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>pannello metallico</v>
       </c>
       <c r="G16" t="str">
         <v>armadio, profile/, block, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, distingue, linee, nette, moderne, perfetta, carattere, deciso</v>
@@ -1361,13 +1406,13 @@
         <v>17</v>
       </c>
       <c r="K16">
-        <v>-171</v>
+        <v>-167.7</v>
       </c>
       <c r="L16">
-        <v>-4</v>
+        <v>-2.2</v>
       </c>
       <c r="M16">
-        <v>70</v>
+        <v>99.4</v>
       </c>
       <c r="N16" t="str">
         <v>BOX 160 - B_161</v>
@@ -1388,12 +1433,15 @@
         <v/>
       </c>
       <c r="T16" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U16" t="str">
+        <v>Telaio Alluminio</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>box-160-b-162-libreria-lapis</v>
+        <v>FEB-016</v>
       </c>
       <c r="B17" t="str">
         <v>Libreria Lapis</v>
@@ -1405,10 +1453,10 @@
         <v>Il sistema libreria Lapis, configurabile a parete e centro stanza, si adatta perfettamente anche ad ambienti giorno e notte regalando estremo rigore e contenimento. Il suo design inedito è personalizzabile grazie a diversi elementi compositivi: ripiani in vetro, in metallo o in pannello, pensili e basi in differenti modularità per soddisfare qualsiasi esigenza.</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>antracite, legno naturale</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>metallo, legno</v>
       </c>
       <c r="G17" t="str">
         <v>libreria, lapis, librerie, librería, librerías, estanteria, estantería, bookshelf, estante, sistema, configurabile, parete, centro, stanza, adatta, perfettamente, ambienti, giorno, notte</v>
@@ -1423,13 +1471,13 @@
         <v>17</v>
       </c>
       <c r="K17">
-        <v>110</v>
+        <v>126.6</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>-2.6</v>
       </c>
       <c r="M17">
-        <v>70</v>
+        <v>86.5</v>
       </c>
       <c r="N17" t="str">
         <v>BOX 160 - B_162</v>
@@ -1447,15 +1495,18 @@
         <v>TRUE</v>
       </c>
       <c r="S17" t="str">
-        <v/>
+        <v>libreria a parete o centro stanza</v>
       </c>
       <c r="T17" t="str">
+        <v>Minimal</v>
+      </c>
+      <c r="U17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>box-160-b-166-pouff-windsor</v>
+        <v>FEB-017</v>
       </c>
       <c r="B18" t="str">
         <v>Pouff Windsor</v>
@@ -1467,10 +1518,10 @@
         <v>Il pouf Windsor completa la gamma dei pouf della collezione divani Febal Casa. Grazie alle dimensioni e ai rivestimenti in cui è disponibile, è un elemento estremamente versatile che risponde a qualsiasi esigenza. La sua leggerezza permette di offrire soluzioni dinamiche per ogni stile di vita.</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>verde oliva scuro</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>tessuto</v>
       </c>
       <c r="G18" t="str">
         <v>pouff, windsor, pouf, puff, puffs, puf, ottoman, reposapies, completa, gamma, collezione, divani, febal, casa, grazie, dimensioni, rivestimenti, disponibile</v>
@@ -1485,13 +1536,13 @@
         <v>17</v>
       </c>
       <c r="K18">
-        <v>32</v>
+        <v>35.9</v>
       </c>
       <c r="L18">
-        <v>-40</v>
+        <v>-38.8</v>
       </c>
       <c r="M18">
-        <v>70</v>
+        <v>75.7</v>
       </c>
       <c r="N18" t="str">
         <v>BOX 160 - B_166</v>
@@ -1512,12 +1563,15 @@
         <v/>
       </c>
       <c r="T18" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>box-160-b-167-boiserie-tv</v>
+        <v>FEB-018</v>
       </c>
       <c r="B19" t="str">
         <v>Boiserie TV</v>
@@ -1547,13 +1601,13 @@
         <v>17</v>
       </c>
       <c r="K19">
-        <v>38</v>
+        <v>49.4</v>
       </c>
       <c r="L19">
-        <v>14</v>
+        <v>8.1</v>
       </c>
       <c r="M19">
-        <v>70</v>
+        <v>90.2</v>
       </c>
       <c r="N19" t="str">
         <v>BOX 160 - B_167</v>
@@ -1574,12 +1628,15 @@
         <v/>
       </c>
       <c r="T19" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>box-170-b-172-sistema-origina</v>
+        <v>FEB-019</v>
       </c>
       <c r="B20" t="str">
         <v>Sistema Origina</v>
@@ -1591,10 +1648,10 @@
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>greige/tortora, marmo nero venato oro</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>legno laccato, marmo</v>
       </c>
       <c r="G20" t="str">
         <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
@@ -1630,18 +1687,21 @@
         <v>sistemi-modulari</v>
       </c>
       <c r="R20" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>cucina componibile a isola</v>
       </c>
       <c r="T20" t="str">
-        <v/>
+        <v>Classico elegante</v>
+      </c>
+      <c r="U20" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>box-170-b-173-sistema-origina</v>
+        <v>FEB-020</v>
       </c>
       <c r="B21" t="str">
         <v>Sistema Origina</v>
@@ -1653,10 +1713,10 @@
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>greige/tortora, marmo nero venato oro</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>legno laccato, marmo</v>
       </c>
       <c r="G21" t="str">
         <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
@@ -1668,16 +1728,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J21" t="str">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K21">
-        <v>-76</v>
+        <v>-175.9</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>-2.4</v>
       </c>
       <c r="M21">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N21" t="str">
         <v>BOX 170 - B_173</v>
@@ -1698,12 +1758,15 @@
         <v/>
       </c>
       <c r="T21" t="str">
-        <v/>
+        <v>Classico elegante</v>
+      </c>
+      <c r="U21" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>box-170-b-174-sistema-origina</v>
+        <v>FEB-021</v>
       </c>
       <c r="B22" t="str">
         <v>Sistema Origina</v>
@@ -1715,10 +1778,10 @@
         <v>L’anta a telaio è simbolo di un uno stile classico che può essere abbinato a aperture a gola, a maniglie e a pomoli.</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>greige/tortora, marmo nero venato oro</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>legno laccato, marmo</v>
       </c>
       <c r="G22" t="str">
         <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, anta, telaio, simbolo, stile, classico, abbinato, aperture, gola, maniglie, pomoli</v>
@@ -1730,16 +1793,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J22" t="str">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22">
-        <v>126</v>
+        <v>-162.4</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>-3.9</v>
       </c>
       <c r="M22">
-        <v>70</v>
+        <v>117.3</v>
       </c>
       <c r="N22" t="str">
         <v>BOX 170 - B_174</v>
@@ -1760,12 +1823,15 @@
         <v/>
       </c>
       <c r="T22" t="str">
-        <v/>
+        <v>Classico elegante</v>
+      </c>
+      <c r="U22" t="str">
+        <v>Laccato Opaco</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>box-180-b-181-armadio-barret-con-portale</v>
+        <v>FEB-022</v>
       </c>
       <c r="B23" t="str">
         <v>Armadio Barret con Portale</v>
@@ -1777,10 +1843,10 @@
         <v>Scopri gli armadi a ponte con passaggio Febal Casa: soluzioni architettoniche che ottimizzano lo spazio con stile e funzionalità.</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>wenge/marrone scurissimo</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>pannello impiallacciato</v>
       </c>
       <c r="G23" t="str">
         <v>armadio, barret, portale, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, scopri, ponte, passaggio, febal, casa, soluzioni, architettoniche, ottimizzano, spazio, stile, funzionalita</v>
@@ -1816,18 +1882,21 @@
         <v>armadi</v>
       </c>
       <c r="R23" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S23" t="str">
-        <v/>
+        <v>armadio con passaggio a ponte</v>
       </c>
       <c r="T23" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>box-180-b-182-libreria-trenta</v>
+        <v>FEB-023</v>
       </c>
       <c r="B24" t="str">
         <v>Libreria Trenta</v>
@@ -1854,16 +1923,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J24" t="str">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K24">
-        <v>75</v>
+        <v>-51.2</v>
       </c>
       <c r="L24">
-        <v>-6</v>
+        <v>-8.1</v>
       </c>
       <c r="M24">
-        <v>70</v>
+        <v>109.2</v>
       </c>
       <c r="N24" t="str">
         <v>BOX 180 - B_182</v>
@@ -1884,12 +1953,15 @@
         <v/>
       </c>
       <c r="T24" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>box-180-b-186-boiserie</v>
+        <v>FEB-024</v>
       </c>
       <c r="B25" t="str">
         <v>Boiserie</v>
@@ -1901,10 +1973,10 @@
         <v>La boiserie è concepita come un sistema in grado di dialogare con tutti gli altri arredi della gamma Febal Casa, un elemento versatile che si innesta con soluzione di continuità arrivando fino a terra.</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>beige chiaro venato</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>pannello effetto pietra</v>
       </c>
       <c r="G25" t="str">
         <v>boiserie, panel, paneles decorativos, revestimiento, pared, decorativo, columna, vertical, concepita, sistema, grado, dialogare, tutti, altri, arredi, gamma, febal, casa, elemento</v>
@@ -1916,16 +1988,16 @@
         <v>CASA 01 - AUTENTICA</v>
       </c>
       <c r="J25" t="str">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K25">
-        <v>-163.96</v>
+        <v>-178.1</v>
       </c>
       <c r="L25">
-        <v>-0.17</v>
+        <v>-7.5</v>
       </c>
       <c r="M25">
-        <v>70</v>
+        <v>101.9</v>
       </c>
       <c r="N25" t="str">
         <v>BOX 180 - B_186</v>
@@ -1943,15 +2015,18 @@
         <v>TRUE</v>
       </c>
       <c r="S25" t="str">
-        <v/>
+        <v>boiserie modulare a tutta altezza</v>
       </c>
       <c r="T25" t="str">
-        <v/>
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U25" t="str">
+        <v>Scenario</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>box-200-b-201-libreria-trenta-anta-libeskind022</v>
+        <v>FEB-025</v>
       </c>
       <c r="B26" t="str">
         <v>Libreria Trenta Anta Libeskind022</v>
@@ -1978,16 +2053,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J26" t="str">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K26">
-        <v>-117</v>
+        <v>147.5</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>-0.2</v>
       </c>
       <c r="M26">
-        <v>70</v>
+        <v>118.2</v>
       </c>
       <c r="N26" t="str">
         <v>BOX 200 - B_201</v>
@@ -2008,12 +2083,15 @@
         <v/>
       </c>
       <c r="T26" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>box-200-b-202-divano-camden</v>
+        <v>FEB-026</v>
       </c>
       <c r="B27" t="str">
         <v>Divano Camden</v>
@@ -2025,7 +2103,7 @@
         <v>Camden unisce eleganza e comfort in un design armonioso e avvolgente. Personalizzabile nei rivestimenti, si adatta a spazi classici e moderni, offrendo stile, calore e funzionalità a ogni ambiente living.</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>verde</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -2064,18 +2142,21 @@
         <v>divani</v>
       </c>
       <c r="R27" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S27" t="str">
-        <v/>
+        <v>modulare con isola</v>
       </c>
       <c r="T27" t="str">
-        <v/>
+        <v>Caldo accogliente, Classico elegante</v>
+      </c>
+      <c r="U27" t="str">
+        <v>Velvet</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>box-200-b-203-divano-camden</v>
+        <v>FEB-027</v>
       </c>
       <c r="B28" t="str">
         <v>Divano Camden</v>
@@ -2087,7 +2168,7 @@
         <v>Camden unisce eleganza e comfort in un design armonioso e avvolgente. Personalizzabile nei rivestimenti, si adatta a spazi classici e moderni, offrendo stile, calore e funzionalità a ogni ambiente living.</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>cognac</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -2102,16 +2183,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J28" t="str">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K28">
-        <v>32</v>
+        <v>-128</v>
       </c>
       <c r="L28">
-        <v>-10</v>
+        <v>-41.6</v>
       </c>
       <c r="M28">
-        <v>70</v>
+        <v>87.8</v>
       </c>
       <c r="N28" t="str">
         <v>BOX 200 - B_203</v>
@@ -2129,15 +2210,18 @@
         <v>TRUE</v>
       </c>
       <c r="S28" t="str">
-        <v/>
+        <v>modulare curvo</v>
       </c>
       <c r="T28" t="str">
-        <v/>
+        <v>Caldo accogliente, Classico elegante</v>
+      </c>
+      <c r="U28" t="str">
+        <v>Boston</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>box-200-b-204-poltrone-astor</v>
+        <v>FEB-028</v>
       </c>
       <c r="B29" t="str">
         <v>Poltrone Astor</v>
@@ -2164,16 +2248,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J29" t="str">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K29">
-        <v>-9</v>
+        <v>-34.5</v>
       </c>
       <c r="L29">
-        <v>-20</v>
+        <v>-26.4</v>
       </c>
       <c r="M29">
-        <v>70</v>
+        <v>67.9</v>
       </c>
       <c r="N29" t="str">
         <v>BOX 200 - B_204</v>
@@ -2194,12 +2278,15 @@
         <v/>
       </c>
       <c r="T29" t="str">
+        <v>Caldo accogliente, Contemporaneo</v>
+      </c>
+      <c r="U29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>box-200-b-205-tavolini-ink</v>
+        <v>FEB-029</v>
       </c>
       <c r="B30" t="str">
         <v>Tavolini Ink</v>
@@ -2229,13 +2316,13 @@
         <v>52</v>
       </c>
       <c r="K30">
-        <v>-12</v>
+        <v>-12.8</v>
       </c>
       <c r="L30">
-        <v>-28</v>
+        <v>-28.5</v>
       </c>
       <c r="M30">
-        <v>70</v>
+        <v>49.8</v>
       </c>
       <c r="N30" t="str">
         <v>BOX 200 - B_205</v>
@@ -2256,12 +2343,15 @@
         <v/>
       </c>
       <c r="T30" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>box-220-b-221-cucina-origina-anta-libeskind022</v>
+        <v>FEB-030</v>
       </c>
       <c r="B31" t="str">
         <v>Cucina Origina Anta Libeskind022</v>
@@ -2270,7 +2360,7 @@
         <v>cucine</v>
       </c>
       <c r="D31" t="str">
-        <v>Cucina Origina Anta Libeskind022 — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
+        <v>Cucina Origina Anta Libeskind022 — elemento della collezione Febal Casa, sezione CASA 02 - PERFETTA.</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -2279,7 +2369,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>cucina, origina, anta, libeskind022, cucine, cocina, cocinas, kitchen, isla, casa, libeskind, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>cucina, origina, anta, libeskind022, cucine, cocina, cocinas, kitchen, isla, casa, libeskind, elemento, collezione, febal, sezione, perfetta</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -2291,13 +2381,13 @@
         <v>61</v>
       </c>
       <c r="K31">
-        <v>-140</v>
+        <v>-120.5</v>
       </c>
       <c r="L31">
-        <v>-30</v>
+        <v>-34.9</v>
       </c>
       <c r="M31">
-        <v>70</v>
+        <v>93.4</v>
       </c>
       <c r="N31" t="str">
         <v>BOX 220 - B_221</v>
@@ -2318,12 +2408,15 @@
         <v/>
       </c>
       <c r="T31" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>box-220-b-222-sistema-origina</v>
+        <v>FEB-031</v>
       </c>
       <c r="B32" t="str">
         <v>Sistema Origina</v>
@@ -2332,7 +2425,7 @@
         <v>sistemi modulari</v>
       </c>
       <c r="D32" t="str">
-        <v>Sistema Origina — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
+        <v>Sistema Origina — elemento della collezione Febal Casa, sezione CASA 02 - PERFETTA.</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -2341,7 +2434,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>sistema, origina, sistemi modulari, sistema modular, sistemas modulares, modular, casa, elemento, collezione, febal, sezione, perfetta</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2353,13 +2446,13 @@
         <v>61</v>
       </c>
       <c r="K32">
-        <v>-143</v>
+        <v>-123.7</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>70</v>
+        <v>69.4</v>
       </c>
       <c r="N32" t="str">
         <v>BOX 220 - B_222</v>
@@ -2380,12 +2473,15 @@
         <v/>
       </c>
       <c r="T32" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>box-220-b-223-pouff-windsor</v>
+        <v>FEB-032</v>
       </c>
       <c r="B33" t="str">
         <v>Pouff Windsor</v>
@@ -2415,13 +2511,13 @@
         <v>61</v>
       </c>
       <c r="K33">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L33">
-        <v>-40</v>
+        <v>-35.4</v>
       </c>
       <c r="M33">
-        <v>70</v>
+        <v>84.9</v>
       </c>
       <c r="N33" t="str">
         <v>BOX 220 - B_223</v>
@@ -2442,12 +2538,15 @@
         <v/>
       </c>
       <c r="T33" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>box-240-b-241-libreria-trenta</v>
+        <v>FEB-033</v>
       </c>
       <c r="B34" t="str">
         <v>Libreria Trenta</v>
@@ -2474,16 +2573,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J34" t="str">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K34">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>-3.1</v>
       </c>
       <c r="M34">
-        <v>70</v>
+        <v>97.9</v>
       </c>
       <c r="N34" t="str">
         <v>BOX 240 - B_241</v>
@@ -2504,12 +2603,15 @@
         <v/>
       </c>
       <c r="T34" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>box-240-b-242-tavolo-phoenix</v>
+        <v>FEB-034</v>
       </c>
       <c r="B35" t="str">
         <v>Tavolo Phoenix</v>
@@ -2536,16 +2638,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J35" t="str">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K35">
-        <v>-18</v>
+        <v>-3.1</v>
       </c>
       <c r="L35">
-        <v>-38</v>
+        <v>-34.9</v>
       </c>
       <c r="M35">
-        <v>70</v>
+        <v>97.9</v>
       </c>
       <c r="N35" t="str">
         <v>BOX 240 - B_242</v>
@@ -2566,12 +2668,15 @@
         <v/>
       </c>
       <c r="T35" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>box-240-b-244-madia-libeskind022</v>
+        <v>FEB-035</v>
       </c>
       <c r="B36" t="str">
         <v>Madia Libeskind022</v>
@@ -2601,13 +2706,13 @@
         <v>55</v>
       </c>
       <c r="K36">
-        <v>158</v>
+        <v>170.7</v>
       </c>
       <c r="L36">
-        <v>-45</v>
+        <v>-31.6</v>
       </c>
       <c r="M36">
-        <v>70</v>
+        <v>98.8</v>
       </c>
       <c r="N36" t="str">
         <v>BOX 240 - B_244</v>
@@ -2628,12 +2733,15 @@
         <v/>
       </c>
       <c r="T36" t="str">
+        <v>Minimal, Contemporaneo</v>
+      </c>
+      <c r="U36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>box-240-b-245-poltrona-vivienne</v>
+        <v>FEB-036</v>
       </c>
       <c r="B37" t="str">
         <v>Poltrona Vivienne</v>
@@ -2660,16 +2768,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J37" t="str">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K37">
-        <v>101</v>
+        <v>-83.5</v>
       </c>
       <c r="L37">
-        <v>-12</v>
+        <v>-28.8</v>
       </c>
       <c r="M37">
-        <v>70</v>
+        <v>93.5</v>
       </c>
       <c r="N37" t="str">
         <v>BOX 240 - B_245</v>
@@ -2690,12 +2798,15 @@
         <v/>
       </c>
       <c r="T37" t="str">
+        <v>Classico elegante, Contemporaneo</v>
+      </c>
+      <c r="U37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>box-260-b-261-armadio-collezione-momenti</v>
+        <v>FEB-037</v>
       </c>
       <c r="B38" t="str">
         <v>Armadio Collezione Momenti.</v>
@@ -2725,13 +2836,13 @@
         <v>66</v>
       </c>
       <c r="K38">
-        <v>-147</v>
+        <v>-112.5</v>
       </c>
       <c r="L38">
-        <v>-2</v>
+        <v>-6.8</v>
       </c>
       <c r="M38">
-        <v>70</v>
+        <v>123.6</v>
       </c>
       <c r="N38" t="str">
         <v>BOX 260 - B_261</v>
@@ -2752,12 +2863,15 @@
         <v/>
       </c>
       <c r="T38" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>box-260-b-264-boiserie</v>
+        <v>FEB-038</v>
       </c>
       <c r="B39" t="str">
         <v>Boiserie</v>
@@ -2787,13 +2901,13 @@
         <v>65</v>
       </c>
       <c r="K39">
-        <v>85</v>
+        <v>85.4</v>
       </c>
       <c r="L39">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="M39">
-        <v>70</v>
+        <v>109.7</v>
       </c>
       <c r="N39" t="str">
         <v>BOX 260 - B_264</v>
@@ -2814,12 +2928,15 @@
         <v/>
       </c>
       <c r="T39" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>box-280-b-281-letto-couple</v>
+        <v>FEB-039</v>
       </c>
       <c r="B40" t="str">
         <v>Letto Couple</v>
@@ -2828,7 +2945,7 @@
         <v>camera da letto</v>
       </c>
       <c r="D40" t="str">
-        <v>Letto Couple — pieza de la colección Febal Casa, sección CASA 02 - PERFETTA.</v>
+        <v>Letto Couple — elemento della collezione Febal Casa, sezione CASA 02 - PERFETTA.</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -2837,7 +2954,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>letto, couple, camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, pieza, coleccion, febal, seccion, perfetta</v>
+        <v>letto, couple, camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, elemento, collezione, febal, sezione, perfetta</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2846,16 +2963,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J40" t="str">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K40">
-        <v>68</v>
+        <v>3.4</v>
       </c>
       <c r="L40">
-        <v>-29</v>
+        <v>-34</v>
       </c>
       <c r="M40">
-        <v>70</v>
+        <v>115.9</v>
       </c>
       <c r="N40" t="str">
         <v>BOX 280 - B_281</v>
@@ -2876,12 +2993,15 @@
         <v/>
       </c>
       <c r="T40" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>box-280-b-284-poltrona-isabelle</v>
+        <v>FEB-040</v>
       </c>
       <c r="B41" t="str">
         <v>Poltrona Isabelle</v>
@@ -2908,16 +3028,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J41" t="str">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K41">
-        <v>89</v>
+        <v>-81.5</v>
       </c>
       <c r="L41">
-        <v>-34</v>
+        <v>-40.1</v>
       </c>
       <c r="M41">
-        <v>70</v>
+        <v>89.3</v>
       </c>
       <c r="N41" t="str">
         <v>BOX 280 - B_284</v>
@@ -2938,12 +3058,15 @@
         <v/>
       </c>
       <c r="T41" t="str">
+        <v>Classico elegante, Contemporaneo</v>
+      </c>
+      <c r="U41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>box-280-b-285-specchio-polar</v>
+        <v>FEB-041</v>
       </c>
       <c r="B42" t="str">
         <v>Specchio Polar</v>
@@ -2973,13 +3096,13 @@
         <v>58</v>
       </c>
       <c r="K42">
-        <v>123</v>
+        <v>136.7</v>
       </c>
       <c r="L42">
-        <v>-10</v>
+        <v>-6.8</v>
       </c>
       <c r="M42">
-        <v>70</v>
+        <v>96.4</v>
       </c>
       <c r="N42" t="str">
         <v>BOX 280 - B_285</v>
@@ -3000,12 +3123,15 @@
         <v/>
       </c>
       <c r="T42" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>box-290-b-291-boiserie</v>
+        <v>FEB-042</v>
       </c>
       <c r="B43" t="str">
         <v>Boiserie</v>
@@ -3032,16 +3158,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J43" t="str">
-        <v>59a</v>
+        <v>59b</v>
       </c>
       <c r="K43">
-        <v>-100</v>
+        <v>-17.1</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M43">
-        <v>70</v>
+        <v>121.6</v>
       </c>
       <c r="N43" t="str">
         <v>BOX 290 - B_291</v>
@@ -3062,12 +3188,15 @@
         <v/>
       </c>
       <c r="T43" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>box-290-b-293-cabina-armadio-lapis</v>
+        <v>FEB-043</v>
       </c>
       <c r="B44" t="str">
         <v>Cabina Armadio Lapis</v>
@@ -3094,16 +3223,16 @@
         <v>CASA 02 - PERFETTA</v>
       </c>
       <c r="J44" t="str">
-        <v>59a</v>
+        <v>59b</v>
       </c>
       <c r="K44">
-        <v>-128</v>
+        <v>-14.1</v>
       </c>
       <c r="L44">
-        <v>-10</v>
+        <v>-14.6</v>
       </c>
       <c r="M44">
-        <v>70</v>
+        <v>121.6</v>
       </c>
       <c r="N44" t="str">
         <v>BOX 290 - B_293</v>
@@ -3124,12 +3253,15 @@
         <v/>
       </c>
       <c r="T44" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>box-290-b-294-boiserie</v>
+        <v>FEB-044</v>
       </c>
       <c r="B45" t="str">
         <v>Boiserie</v>
@@ -3180,18 +3312,21 @@
         <v>boiserie</v>
       </c>
       <c r="R45" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S45" t="str">
         <v/>
       </c>
       <c r="T45" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>box-290-b-295-armadio-lewitt-plus</v>
+        <v>FEB-045</v>
       </c>
       <c r="B46" t="str">
         <v>Armadio Lewitt Plus</v>
@@ -3221,13 +3356,13 @@
         <v>59a</v>
       </c>
       <c r="K46">
-        <v>136</v>
+        <v>133.2</v>
       </c>
       <c r="L46">
-        <v>-2</v>
+        <v>-5.3</v>
       </c>
       <c r="M46">
-        <v>70</v>
+        <v>121.6</v>
       </c>
       <c r="N46" t="str">
         <v>BOX 290 - B_295</v>
@@ -3248,12 +3383,15 @@
         <v/>
       </c>
       <c r="T46" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>box-300-b-301-sistema-diciotto</v>
+        <v>FEB-046</v>
       </c>
       <c r="B47" t="str">
         <v>Sistema Diciotto</v>
@@ -3280,16 +3418,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J47" t="str">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K47">
-        <v>-120</v>
+        <v>-179.3</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>-6.2</v>
       </c>
       <c r="M47">
-        <v>70</v>
+        <v>86.7</v>
       </c>
       <c r="N47" t="str">
         <v>BOX 300 - B_301</v>
@@ -3310,12 +3448,15 @@
         <v/>
       </c>
       <c r="T47" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>box-300-b-302-libreria-trenta</v>
+        <v>FEB-047</v>
       </c>
       <c r="B48" t="str">
         <v>Libreria Trenta</v>
@@ -3342,16 +3483,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J48" t="str">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K48">
-        <v>160</v>
+        <v>10.2</v>
       </c>
       <c r="L48">
-        <v>13</v>
+        <v>2.8</v>
       </c>
       <c r="M48">
-        <v>70</v>
+        <v>98.3</v>
       </c>
       <c r="N48" t="str">
         <v>BOX 300 - B_302</v>
@@ -3372,12 +3513,15 @@
         <v/>
       </c>
       <c r="T48" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>box-300-b-303-divano-melrose</v>
+        <v>FEB-048</v>
       </c>
       <c r="B49" t="str">
         <v>Divano Melrose</v>
@@ -3404,16 +3548,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J49" t="str">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K49">
-        <v>130</v>
+        <v>38.3</v>
       </c>
       <c r="L49">
-        <v>-15</v>
+        <v>-36.5</v>
       </c>
       <c r="M49">
-        <v>70</v>
+        <v>86.9</v>
       </c>
       <c r="N49" t="str">
         <v>BOX 300 - B_303</v>
@@ -3434,12 +3578,15 @@
         <v>ad angolo</v>
       </c>
       <c r="T49" t="str">
+        <v>Caldo accogliente, Contemporaneo</v>
+      </c>
+      <c r="U49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>box-300-b-304-poltrona-andy</v>
+        <v>FEB-049</v>
       </c>
       <c r="B50" t="str">
         <v>Poltrona Andy</v>
@@ -3469,13 +3616,13 @@
         <v>42</v>
       </c>
       <c r="K50">
-        <v>-154</v>
+        <v>-172.5</v>
       </c>
       <c r="L50">
-        <v>-31</v>
+        <v>-44.8</v>
       </c>
       <c r="M50">
-        <v>70</v>
+        <v>86.1</v>
       </c>
       <c r="N50" t="str">
         <v>BOX 300 - B_304</v>
@@ -3496,12 +3643,15 @@
         <v/>
       </c>
       <c r="T50" t="str">
+        <v>Contemporaneo, Caldo accogliente</v>
+      </c>
+      <c r="U50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>box-300-b-308-gruppo-notte-marlene</v>
+        <v>FEB-050</v>
       </c>
       <c r="B51" t="str">
         <v>Gruppo Notte Marlene</v>
@@ -3528,16 +3678,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J51" t="str">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K51">
-        <v>-55</v>
+        <v>-69.7</v>
       </c>
       <c r="L51">
-        <v>-30</v>
+        <v>-22.3</v>
       </c>
       <c r="M51">
-        <v>70</v>
+        <v>78.2</v>
       </c>
       <c r="N51" t="str">
         <v>BOX 300 - B_308</v>
@@ -3558,12 +3708,15 @@
         <v/>
       </c>
       <c r="T51" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>box-320-b-321-cucina-modula-anta-square</v>
+        <v>FEB-051</v>
       </c>
       <c r="B52" t="str">
         <v>Cucina Modula anta Square</v>
@@ -3572,7 +3725,7 @@
         <v>cucine</v>
       </c>
       <c r="D52" t="str">
-        <v>Cucina Modula anta Square — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>Cucina Modula anta Square — elemento della collezione Febal Casa, sezione CASA 03 - AUDACE.</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -3581,7 +3734,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>cucina, modula, anta, square, cucine, cocina, cocinas, kitchen, isla, casa, pieza, coleccion, febal, seccion, audace</v>
+        <v>cucina, modula, anta, square, cucine, cocina, cocinas, kitchen, isla, casa, elemento, collezione, febal, sezione, audace</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -3590,16 +3743,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J52" t="str">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K52">
-        <v>52</v>
+        <v>98.9</v>
       </c>
       <c r="L52">
-        <v>3</v>
+        <v>-8.3</v>
       </c>
       <c r="M52">
-        <v>70</v>
+        <v>114.7</v>
       </c>
       <c r="N52" t="str">
         <v>BOX 320 - B_321</v>
@@ -3620,12 +3773,15 @@
         <v/>
       </c>
       <c r="T52" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>box-320-b-322-tavolo-madeira</v>
+        <v>FEB-052</v>
       </c>
       <c r="B53" t="str">
         <v>Tavolo Madeira</v>
@@ -3634,16 +3790,16 @@
         <v>tavoli</v>
       </c>
       <c r="D53" t="str">
-        <v>Tavolo Madeira — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>L'armonioso intreccio di archi definisce un tavolo unico, protagonista di ogni ambiente. Le gambe inclinate e sovrapposte formano un disegno geometrico di grande impatto visivo che gioca con la tridimensionalità ottenendo un risultato perfetto nato dall'eleganza, dall'equilibrio e dalla leggerezza dei volumi. La base in metallo è disponibile in finitura Ottone Scuro, Nero, Antracite e Sabbia. Il piano è di forma rotonda, ovale fisso o allungabile ed è configurabile in Cristallo Lucido, Cristallo Velvet, Superceramica, Supermarmo opaco, Supermarmo lucido e legno Impiallacciato. La versione fissa può essere arricchita con il piano centrotavola girevole, un dispositivo rotante che permette di condividere facilmente cibi e oggetti con tutti i commensali.</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>antracite</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>supermarmo lucido, metallo</v>
       </c>
       <c r="G53" t="str">
-        <v>tavolo, madeira, tavoli, mesa, mesas, table, comedor, casa, pieza, coleccion, febal, seccion, audace</v>
+        <v>tavolo, madeira, tavoli, mesa, mesas, table, comedor, dall, piano, cristallo, lucido, supermarmo, armonioso, intreccio, archi, definisce, unico, protagonista</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -3655,22 +3811,22 @@
         <v>97</v>
       </c>
       <c r="K53">
-        <v>100</v>
+        <v>89.6</v>
       </c>
       <c r="L53">
-        <v>-41</v>
+        <v>-38.4</v>
       </c>
       <c r="M53">
-        <v>70</v>
+        <v>75.3</v>
       </c>
       <c r="N53" t="str">
         <v>BOX 320 - B_322</v>
       </c>
       <c r="O53" t="str">
-        <v>assets/febal-casa/placeholder-product.png</v>
+        <v>assets/febal-casa/products/madeira.jpg</v>
       </c>
       <c r="P53" t="str">
-        <v xml:space="preserve">https://www.febalcasa.com/it/prodotti/madeira/ </v>
+        <v>https://www.febalcasa.com/it/prodotti/madeira/</v>
       </c>
       <c r="Q53" t="str">
         <v>tavoli</v>
@@ -3679,15 +3835,18 @@
         <v>TRUE</v>
       </c>
       <c r="S53" t="str">
-        <v/>
+        <v>rotondo o ovale, fisso o allungabile</v>
       </c>
       <c r="T53" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>box-320-b-323-sedia-nina</v>
+        <v>FEB-053</v>
       </c>
       <c r="B54" t="str">
         <v>Sedia Nina</v>
@@ -3717,13 +3876,13 @@
         <v>97</v>
       </c>
       <c r="K54">
-        <v>40</v>
+        <v>34.6</v>
       </c>
       <c r="L54">
-        <v>-40</v>
+        <v>-42.6</v>
       </c>
       <c r="M54">
-        <v>70</v>
+        <v>75.3</v>
       </c>
       <c r="N54" t="str">
         <v>BOX 320 - B_323</v>
@@ -3744,12 +3903,15 @@
         <v/>
       </c>
       <c r="T54" t="str">
+        <v>Caldo accogliente</v>
+      </c>
+      <c r="U54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>box-320-b-324-madia-leaf</v>
+        <v>FEB-054</v>
       </c>
       <c r="B55" t="str">
         <v>Madia Leaf</v>
@@ -3776,16 +3938,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J55" t="str">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="K55">
-        <v>-17.02</v>
+        <v>-109.2</v>
       </c>
       <c r="L55">
-        <v>-8.24</v>
+        <v>-41</v>
       </c>
       <c r="M55">
-        <v>70</v>
+        <v>98.4</v>
       </c>
       <c r="N55" t="str">
         <v>BOX 320 - B_324</v>
@@ -3806,12 +3968,15 @@
         <v/>
       </c>
       <c r="T55" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>box-340-b-342-libreria-trenta</v>
+        <v>FEB-055</v>
       </c>
       <c r="B56" t="str">
         <v>Libreria Trenta</v>
@@ -3841,13 +4006,13 @@
         <v>47</v>
       </c>
       <c r="K56">
-        <v>-23</v>
+        <v>-36.4</v>
       </c>
       <c r="L56">
-        <v>-17</v>
+        <v>-5.4</v>
       </c>
       <c r="M56">
-        <v>70</v>
+        <v>110.2</v>
       </c>
       <c r="N56" t="str">
         <v>BOX 340 - B_342</v>
@@ -3868,12 +4033,15 @@
         <v/>
       </c>
       <c r="T56" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>box-340-b-344-gruppo-notte-marlene</v>
+        <v>FEB-056</v>
       </c>
       <c r="B57" t="str">
         <v>Gruppo Notte Marlene</v>
@@ -3900,16 +4068,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J57" t="str">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K57">
-        <v>127</v>
+        <v>115.5</v>
       </c>
       <c r="L57">
-        <v>-37</v>
+        <v>-29.6</v>
       </c>
       <c r="M57">
-        <v>70</v>
+        <v>54.4</v>
       </c>
       <c r="N57" t="str">
         <v>BOX 340 - B_344</v>
@@ -3930,12 +4098,15 @@
         <v/>
       </c>
       <c r="T57" t="str">
+        <v>Contemporaneo, Classico elegante</v>
+      </c>
+      <c r="U57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>box-340-b-345-boiserie</v>
+        <v>FEB-057</v>
       </c>
       <c r="B58" t="str">
         <v>Boiserie</v>
@@ -3962,16 +4133,16 @@
         <v>CASA 03 - AUDACE</v>
       </c>
       <c r="J58" t="str">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K58">
-        <v>139</v>
+        <v>110.6</v>
       </c>
       <c r="L58">
-        <v>-21</v>
+        <v>-15.3</v>
       </c>
       <c r="M58">
-        <v>70</v>
+        <v>69.6</v>
       </c>
       <c r="N58" t="str">
         <v>BOX 340 - B_345</v>
@@ -3992,12 +4163,15 @@
         <v/>
       </c>
       <c r="T58" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>box-360-b-361-armadio-collezione-momenti</v>
+        <v>FEB-058</v>
       </c>
       <c r="B59" t="str">
         <v>Armadio Collezione Momenti.</v>
@@ -4006,7 +4180,7 @@
         <v>armadi</v>
       </c>
       <c r="D59" t="str">
-        <v>Armadio Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>Armadio Collezione Momenti. — elemento della collezione Febal Casa, sezione CASA 03 - AUDACE.</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -4015,7 +4189,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, elemento, febal, sezione, audace</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -4027,13 +4201,13 @@
         <v>92</v>
       </c>
       <c r="K59">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>-2.2</v>
       </c>
       <c r="M59">
-        <v>70</v>
+        <v>74.5</v>
       </c>
       <c r="N59" t="str">
         <v>BOX 360 - B_361</v>
@@ -4054,12 +4228,15 @@
         <v/>
       </c>
       <c r="T59" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>box-360-b-362-letto-collezione-momenti</v>
+        <v>FEB-059</v>
       </c>
       <c r="B60" t="str">
         <v>Letto Collezione Momenti.</v>
@@ -4068,7 +4245,7 @@
         <v>camera da letto</v>
       </c>
       <c r="D60" t="str">
-        <v>Letto Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>Letto Collezione Momenti. — elemento della collezione Febal Casa, sezione CASA 03 - AUDACE.</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -4077,7 +4254,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>letto, collezione, momenti., camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>letto, collezione, momenti., camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, casa, momenti, elemento, febal, sezione, audace</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -4089,13 +4266,13 @@
         <v>92</v>
       </c>
       <c r="K60">
-        <v>165</v>
+        <v>173.8</v>
       </c>
       <c r="L60">
-        <v>-28</v>
+        <v>-22.7</v>
       </c>
       <c r="M60">
-        <v>70</v>
+        <v>91.7</v>
       </c>
       <c r="N60" t="str">
         <v>BOX 360 - B_362</v>
@@ -4116,12 +4293,15 @@
         <v/>
       </c>
       <c r="T60" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>box-360-b-363-libreria-collezione-momenti</v>
+        <v>FEB-060</v>
       </c>
       <c r="B61" t="str">
         <v>Libreria Collezione Momenti.</v>
@@ -4130,7 +4310,7 @@
         <v>librerie</v>
       </c>
       <c r="D61" t="str">
-        <v>Libreria Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>Libreria Collezione Momenti. — elemento della collezione Febal Casa, sezione CASA 03 - AUDACE.</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -4139,7 +4319,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>libreria, collezione, momenti., librerie, librería, librerías, estanteria, estantería, bookshelf, estante, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>libreria, collezione, momenti., librerie, librería, librerías, estanteria, estantería, bookshelf, estante, casa, momenti, elemento, febal, sezione, audace</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -4151,13 +4331,13 @@
         <v>92</v>
       </c>
       <c r="K61">
-        <v>35</v>
+        <v>7.4</v>
       </c>
       <c r="L61">
-        <v>10</v>
+        <v>-3.8</v>
       </c>
       <c r="M61">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N61" t="str">
         <v>BOX 360 - B_363</v>
@@ -4178,12 +4358,15 @@
         <v/>
       </c>
       <c r="T61" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>box-360-b-364-pouff-windsor</v>
+        <v>FEB-061</v>
       </c>
       <c r="B62" t="str">
         <v>Pouff Windsor</v>
@@ -4213,13 +4396,13 @@
         <v>92</v>
       </c>
       <c r="K62">
-        <v>132</v>
+        <v>127.6</v>
       </c>
       <c r="L62">
-        <v>-22</v>
+        <v>-23.3</v>
       </c>
       <c r="M62">
-        <v>70</v>
+        <v>53.8</v>
       </c>
       <c r="N62" t="str">
         <v>BOX 360 - B_364</v>
@@ -4240,21 +4423,24 @@
         <v/>
       </c>
       <c r="T62" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>box-360-b-365-armadio-collezione-momenti</v>
+        <v>FEB-062</v>
       </c>
       <c r="B63" t="str">
-        <v>Armadio  Collezione Momenti.</v>
+        <v>Armadio Collezione Momenti.</v>
       </c>
       <c r="C63" t="str">
         <v>armadi</v>
       </c>
       <c r="D63" t="str">
-        <v>Armadio  Collezione Momenti. — pieza de la colección Febal Casa, sección CASA 03 - AUDACE.</v>
+        <v>Armadio Collezione Momenti. — elemento della collezione Febal Casa, sezione CASA 03 - AUDACE.</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -4263,7 +4449,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, pieza, coleccion, febal, seccion, audace</v>
+        <v>armadio, collezione, momenti., armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, casa, momenti, elemento, febal, sezione, audace</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -4296,18 +4482,21 @@
         <v>armadi</v>
       </c>
       <c r="R63" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S63" t="str">
         <v/>
       </c>
       <c r="T63" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>box-400-b-401-boiserie</v>
+        <v>FEB-063</v>
       </c>
       <c r="B64" t="str">
         <v>Boiserie</v>
@@ -4337,13 +4526,13 @@
         <v>76</v>
       </c>
       <c r="K64">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="L64">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="M64">
-        <v>70</v>
+        <v>80.4</v>
       </c>
       <c r="N64" t="str">
         <v>BOX 400 - B_401</v>
@@ -4364,12 +4553,15 @@
         <v/>
       </c>
       <c r="T64" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>box-400-b-401-libreria-trenta</v>
+        <v>FEB-064</v>
       </c>
       <c r="B65" t="str">
         <v>Libreria Trenta</v>
@@ -4396,16 +4588,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J65" t="str">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K65">
-        <v>-58</v>
+        <v>43.8</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>-2.9</v>
       </c>
       <c r="M65">
-        <v>70</v>
+        <v>102.7</v>
       </c>
       <c r="N65" t="str">
         <v>BOX 400 - B_401</v>
@@ -4426,12 +4618,15 @@
         <v/>
       </c>
       <c r="T65" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>box-400-b-402-madia-onda-zaha-hadid-architects</v>
+        <v>FEB-065</v>
       </c>
       <c r="B66" t="str">
         <v>Madia Onda - Zaha Hadid Architects</v>
@@ -4440,7 +4635,7 @@
         <v>madie</v>
       </c>
       <c r="D66" t="str">
-        <v>Madia Onda - Zaha Hadid Architects — pieza de la colección Febal Casa, sección CASA 04 - A-MARE.</v>
+        <v>Madia Onda - Zaha Hadid Architects — elemento della collezione Febal Casa, sezione CASA 04 - A-MARE.</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -4449,7 +4644,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>madia, onda, zaha, hadid, architects, madie, aparador, aparadores, credenza, sideboard, buffet, casa, pieza, coleccion, febal, seccion, mare</v>
+        <v>madia, onda, zaha, hadid, architects, madie, aparador, aparadores, credenza, sideboard, buffet, casa, elemento, collezione, febal, sezione, mare</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -4458,16 +4653,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J66" t="str">
-        <v>72</v>
+        <v>74a</v>
       </c>
       <c r="K66">
-        <v>-115</v>
+        <v>50.9</v>
       </c>
       <c r="L66">
-        <v>-23</v>
+        <v>-11</v>
       </c>
       <c r="M66">
-        <v>70</v>
+        <v>47.4</v>
       </c>
       <c r="N66" t="str">
         <v>BOX 400 - B_402</v>
@@ -4488,12 +4683,15 @@
         <v/>
       </c>
       <c r="T66" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>box-400-b-403-divano-navigli</v>
+        <v>FEB-066</v>
       </c>
       <c r="B67" t="str">
         <v>Divano Navigli</v>
@@ -4520,16 +4718,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J67" t="str">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K67">
-        <v>-105</v>
+        <v>-75.9</v>
       </c>
       <c r="L67">
-        <v>-30</v>
+        <v>-38.7</v>
       </c>
       <c r="M67">
-        <v>70</v>
+        <v>95.4</v>
       </c>
       <c r="N67" t="str">
         <v>BOX 400 - B_403</v>
@@ -4550,12 +4748,15 @@
         <v/>
       </c>
       <c r="T67" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>box-420-b-421-libreria-lapis</v>
+        <v>FEB-067</v>
       </c>
       <c r="B68" t="str">
         <v>Libreria Lapis</v>
@@ -4582,16 +4783,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J68" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K68">
-        <v>50</v>
+        <v>-18.4</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>-6.3</v>
       </c>
       <c r="M68">
-        <v>70</v>
+        <v>99.6</v>
       </c>
       <c r="N68" t="str">
         <v>BOX 420 - B_421</v>
@@ -4612,12 +4813,15 @@
         <v/>
       </c>
       <c r="T68" t="str">
+        <v>Minimal</v>
+      </c>
+      <c r="U68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>box-420-b-422-sistema-origina</v>
+        <v>FEB-068</v>
       </c>
       <c r="B69" t="str">
         <v>Sistema Origina</v>
@@ -4644,16 +4848,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J69" t="str">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K69">
-        <v>112</v>
+        <v>-112</v>
       </c>
       <c r="L69">
-        <v>-2</v>
+        <v>-8.3</v>
       </c>
       <c r="M69">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="N69" t="str">
         <v>BOX 420 - B_422</v>
@@ -4674,12 +4878,15 @@
         <v/>
       </c>
       <c r="T69" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>box-420-b-423-cucina-origina-anta-sagoma-37</v>
+        <v>FEB-069</v>
       </c>
       <c r="B70" t="str">
         <v>Cucina Origina Anta Sagoma 37</v>
@@ -4706,16 +4913,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J70" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K70">
-        <v>115</v>
+        <v>-118.3</v>
       </c>
       <c r="L70">
-        <v>-22</v>
+        <v>-34.9</v>
       </c>
       <c r="M70">
-        <v>70</v>
+        <v>90.6</v>
       </c>
       <c r="N70" t="str">
         <v>BOX 420 - B_423</v>
@@ -4736,12 +4943,15 @@
         <v/>
       </c>
       <c r="T70" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>box-420-b-424-cucina-origina-anta-sagoma-37</v>
+        <v>FEB-070</v>
       </c>
       <c r="B71" t="str">
         <v>Cucina Origina Anta Sagoma 37</v>
@@ -4792,18 +5002,21 @@
         <v>cucine</v>
       </c>
       <c r="R71" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S71" t="str">
         <v/>
       </c>
       <c r="T71" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>box-440-b-441-boiserie</v>
+        <v>FEB-071</v>
       </c>
       <c r="B72" t="str">
         <v>Boiserie</v>
@@ -4854,18 +5067,21 @@
         <v>boiserie</v>
       </c>
       <c r="R72" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S72" t="str">
         <v/>
       </c>
       <c r="T72" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>box-440-b-442-tavolo-leeds</v>
+        <v>FEB-072</v>
       </c>
       <c r="B73" t="str">
         <v>Tavolo Leeds</v>
@@ -4892,16 +5108,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J73" t="str">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K73">
-        <v>146</v>
+        <v>-87.6</v>
       </c>
       <c r="L73">
-        <v>-12</v>
+        <v>-26.2</v>
       </c>
       <c r="M73">
-        <v>70</v>
+        <v>74.5</v>
       </c>
       <c r="N73" t="str">
         <v>BOX 440 - B_442</v>
@@ -4922,12 +5138,15 @@
         <v/>
       </c>
       <c r="T73" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>box-440-b-443-sedia-nives-con-braccioli</v>
+        <v>FEB-073</v>
       </c>
       <c r="B74" t="str">
         <v>Sedia Nives con braccioli</v>
@@ -4954,16 +5173,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J74" t="str">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K74">
-        <v>138</v>
+        <v>-50.9</v>
       </c>
       <c r="L74">
-        <v>-19</v>
+        <v>-28.6</v>
       </c>
       <c r="M74">
-        <v>70</v>
+        <v>64.1</v>
       </c>
       <c r="N74" t="str">
         <v>BOX 440 - B_443</v>
@@ -4984,12 +5203,15 @@
         <v/>
       </c>
       <c r="T74" t="str">
+        <v>Classico elegante, Caldo accogliente</v>
+      </c>
+      <c r="U74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>box-460-b-461-armadio-scorrevole-rodin</v>
+        <v>FEB-074</v>
       </c>
       <c r="B75" t="str">
         <v>Armadio Scorrevole Rodin</v>
@@ -5016,16 +5238,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J75" t="str">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K75">
-        <v>-130</v>
+        <v>-8.6</v>
       </c>
       <c r="L75">
-        <v>2</v>
+        <v>-2.9</v>
       </c>
       <c r="M75">
-        <v>70</v>
+        <v>123.1</v>
       </c>
       <c r="N75" t="str">
         <v>BOX 460 - B_461</v>
@@ -5046,12 +5268,15 @@
         <v/>
       </c>
       <c r="T75" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>box-460-b-465-cabina-armadio-hype</v>
+        <v>FEB-075</v>
       </c>
       <c r="B76" t="str">
         <v>Cabina Armadio Hype</v>
@@ -5081,13 +5306,13 @@
         <v>74</v>
       </c>
       <c r="K76">
-        <v>43</v>
+        <v>37.4</v>
       </c>
       <c r="L76">
-        <v>-2</v>
+        <v>-6.4</v>
       </c>
       <c r="M76">
-        <v>70</v>
+        <v>114.1</v>
       </c>
       <c r="N76" t="str">
         <v>BOX 460 - B_465</v>
@@ -5108,12 +5333,15 @@
         <v/>
       </c>
       <c r="T76" t="str">
+        <v>Minimal</v>
+      </c>
+      <c r="U76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>box-500-b-501-isola-onda-zaha-hadid-architects</v>
+        <v>FEB-076</v>
       </c>
       <c r="B77" t="str">
         <v>Isola Onda - Zaha Hadid Architects</v>
@@ -5122,7 +5350,7 @@
         <v>cucine</v>
       </c>
       <c r="D77" t="str">
-        <v>Isola Onda - Zaha Hadid Architects — pieza de la colección Febal Casa, sección CASA 04 - A-MARE.</v>
+        <v>Isola Onda - Zaha Hadid Architects — elemento della collezione Febal Casa, sezione CASA 04 - A-MARE.</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -5131,7 +5359,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>isola, onda, zaha, hadid, architects, cucine, cocina, cocinas, cucina, kitchen, isla, casa, pieza, coleccion, febal, seccion, mare</v>
+        <v>isola, onda, zaha, hadid, architects, cucine, cocina, cocinas, cucina, kitchen, isla, casa, elemento, collezione, febal, sezione, mare</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -5140,16 +5368,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J77" t="str">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K77">
-        <v>92</v>
+        <v>5.5</v>
       </c>
       <c r="L77">
-        <v>-25</v>
+        <v>-17.7</v>
       </c>
       <c r="M77">
-        <v>70</v>
+        <v>57.6</v>
       </c>
       <c r="N77" t="str">
         <v>BOX 500 - B_501</v>
@@ -5170,12 +5398,15 @@
         <v/>
       </c>
       <c r="T77" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>box-500-b-502-sistema-origina-anta-square</v>
+        <v>FEB-077</v>
       </c>
       <c r="B78" t="str">
         <v>Sistema Origina anta Square</v>
@@ -5202,16 +5433,16 @@
         <v>CASA 04 - A-MARE</v>
       </c>
       <c r="J78" t="str">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K78">
-        <v>26</v>
+        <v>10.2</v>
       </c>
       <c r="L78">
-        <v>-15</v>
+        <v>0.2</v>
       </c>
       <c r="M78">
-        <v>70</v>
+        <v>83.6</v>
       </c>
       <c r="N78" t="str">
         <v>BOX 500 - B_502</v>
@@ -5232,12 +5463,15 @@
         <v/>
       </c>
       <c r="T78" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>box-500-b-503-sistema-origina-anta-square</v>
+        <v>FEB-078</v>
       </c>
       <c r="B79" t="str">
         <v>Sistema Origina anta Square</v>
@@ -5288,18 +5522,21 @@
         <v>sistemi-modulari</v>
       </c>
       <c r="R79" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S79" t="str">
         <v/>
       </c>
       <c r="T79" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>box-600-b-601-armadio-profile-leather</v>
+        <v>FEB-079</v>
       </c>
       <c r="B80" t="str">
         <v>Armadio Profile/ Leather</v>
@@ -5329,13 +5566,13 @@
         <v>26</v>
       </c>
       <c r="K80">
-        <v>-58</v>
+        <v>-64.3</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>-2.6</v>
       </c>
       <c r="M80">
-        <v>70</v>
+        <v>90.2</v>
       </c>
       <c r="N80" t="str">
         <v>BOX 600 - B_601</v>
@@ -5356,12 +5593,15 @@
         <v/>
       </c>
       <c r="T80" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>box-600-b-602-armadio-profile-leather</v>
+        <v>FEB-080</v>
       </c>
       <c r="B81" t="str">
         <v>Armadio Profile/ Leather</v>
@@ -5412,18 +5652,21 @@
         <v>armadi</v>
       </c>
       <c r="R81" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S81" t="str">
         <v/>
       </c>
       <c r="T81" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>box-600-b-603-armadio-profile-solid</v>
+        <v>FEB-081</v>
       </c>
       <c r="B82" t="str">
         <v>Armadio Profile/ Solid</v>
@@ -5450,16 +5693,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J82" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K82">
-        <v>85</v>
+        <v>153.6</v>
       </c>
       <c r="L82">
-        <v>1</v>
+        <v>-1.7</v>
       </c>
       <c r="M82">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N82" t="str">
         <v>BOX 600 - B_603</v>
@@ -5480,12 +5723,15 @@
         <v/>
       </c>
       <c r="T82" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>box-600-b-604-armadio-profile-solid</v>
+        <v>FEB-082</v>
       </c>
       <c r="B83" t="str">
         <v>Armadio Profile/ Solid</v>
@@ -5536,18 +5782,21 @@
         <v>armadi</v>
       </c>
       <c r="R83" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S83" t="str">
         <v/>
       </c>
       <c r="T83" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>box-600-b-605-armadio-profile-reflex</v>
+        <v>FEB-083</v>
       </c>
       <c r="B84" t="str">
         <v>Armadio Profile/ Reflex</v>
@@ -5577,13 +5826,13 @@
         <v>31</v>
       </c>
       <c r="K84">
-        <v>-179</v>
+        <v>-177.3</v>
       </c>
       <c r="L84">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
       <c r="M84">
-        <v>70</v>
+        <v>63.7</v>
       </c>
       <c r="N84" t="str">
         <v>BOX 600 - B_605</v>
@@ -5604,12 +5853,15 @@
         <v/>
       </c>
       <c r="T84" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>box-600-b-607-armadio-battente-aurora</v>
+        <v>FEB-084</v>
       </c>
       <c r="B85" t="str">
         <v>Armadio battente Aurora</v>
@@ -5636,16 +5888,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J85" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K85">
-        <v>-92</v>
+        <v>-5.6</v>
       </c>
       <c r="L85">
-        <v>3</v>
+        <v>-9.3</v>
       </c>
       <c r="M85">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N85" t="str">
         <v>BOX 600 - B_607</v>
@@ -5666,12 +5918,15 @@
         <v/>
       </c>
       <c r="T85" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>box-620-b-621-cucina-anta-telaio-alluminio-vetro</v>
+        <v>FEB-085</v>
       </c>
       <c r="B86" t="str">
         <v>Cucina Anta Telaio Alluminio vetro</v>
@@ -5698,16 +5953,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J86" t="str">
-        <v>31</v>
+        <v>80-opening</v>
       </c>
       <c r="K86">
-        <v>18</v>
+        <v>19.3</v>
       </c>
       <c r="L86">
-        <v>-15</v>
+        <v>-30.5</v>
       </c>
       <c r="M86">
-        <v>70</v>
+        <v>87.6</v>
       </c>
       <c r="N86" t="str">
         <v>BOX 620 - B_621</v>
@@ -5728,12 +5983,15 @@
         <v/>
       </c>
       <c r="T86" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>box-620-b-622-armadio-barret</v>
+        <v>FEB-086</v>
       </c>
       <c r="B87" t="str">
         <v>Armadio Barret</v>
@@ -5760,16 +6018,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J87" t="str">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="K87">
-        <v>-27</v>
+        <v>31.4</v>
       </c>
       <c r="L87">
-        <v>2</v>
+        <v>-6.3</v>
       </c>
       <c r="M87">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N87" t="str">
         <v>BOX 620 - B_622</v>
@@ -5790,12 +6048,15 @@
         <v/>
       </c>
       <c r="T87" t="str">
+        <v>Minimal</v>
+      </c>
+      <c r="U87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>box-620-b-623-sgabello-lola</v>
+        <v>FEB-087</v>
       </c>
       <c r="B88" t="str">
         <v>Sgabello Lola</v>
@@ -5825,13 +6086,13 @@
         <v>31</v>
       </c>
       <c r="K88">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="L88">
-        <v>-29</v>
+        <v>-32.4</v>
       </c>
       <c r="M88">
-        <v>70</v>
+        <v>67.3</v>
       </c>
       <c r="N88" t="str">
         <v>BOX 620 - B_623</v>
@@ -5852,12 +6113,15 @@
         <v/>
       </c>
       <c r="T88" t="str">
+        <v>Caldo accogliente, Minimal</v>
+      </c>
+      <c r="U88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>box-640-b-641-armadio-lumia</v>
+        <v>FEB-088</v>
       </c>
       <c r="B89" t="str">
         <v>Armadio Lumia</v>
@@ -5887,13 +6151,13 @@
         <v>88-open</v>
       </c>
       <c r="K89">
-        <v>55</v>
+        <v>-116.8</v>
       </c>
       <c r="L89">
-        <v>-2</v>
+        <v>0.4</v>
       </c>
       <c r="M89">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N89" t="str">
         <v>BOX 640 - B_641</v>
@@ -5914,12 +6178,15 @@
         <v/>
       </c>
       <c r="T89" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>box-640-b-642-armadio-lumia</v>
+        <v>FEB-089</v>
       </c>
       <c r="B90" t="str">
         <v>Armadio Lumia</v>
@@ -5970,18 +6237,21 @@
         <v>armadi</v>
       </c>
       <c r="R90" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="S90" t="str">
         <v/>
       </c>
       <c r="T90" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>box-640-b-643-armadio-lewitt-plus</v>
+        <v>FEB-090</v>
       </c>
       <c r="B91" t="str">
         <v>Armadio Lewitt Plus</v>
@@ -6008,16 +6278,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J91" t="str">
-        <v>85</v>
+        <v>86-open</v>
       </c>
       <c r="K91">
-        <v>163</v>
+        <v>157.3</v>
       </c>
       <c r="L91">
-        <v>-4</v>
+        <v>-12.2</v>
       </c>
       <c r="M91">
-        <v>70</v>
+        <v>103.1</v>
       </c>
       <c r="N91" t="str">
         <v>BOX 640 - B_643</v>
@@ -6038,12 +6308,15 @@
         <v/>
       </c>
       <c r="T91" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>box-640-b-644-tavolo-madeira</v>
+        <v>FEB-091</v>
       </c>
       <c r="B92" t="str">
         <v>Tavolo Madeira</v>
@@ -6055,10 +6328,10 @@
         <v>L'armonioso intreccio di archi definisce un tavolo unico, protagonista di ogni ambiente. Le gambe inclinate e sovrapposte formano un disegno geometrico di grande impatto visivo che gioca con la tridimensionalità ottenendo un risultato perfetto nato dall'eleganza, dall'equilibrio e dalla leggerezza dei volumi. La base in metallo è disponibile in finitura Ottone Scuro, Nero, Antracite e Sabbia. Il piano è di forma rotonda, ovale fisso o allungabile ed è configurabile in Cristallo Lucido, Cristallo Velvet, Superceramica, Supermarmo opaco, Supermarmo lucido e legno Impiallacciato. La versione fissa può essere arricchita con il piano centrotavola girevole, un dispositivo rotante che permette di condividere facilmente cibi e oggetti con tutti i commensali.</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>bianco/sabbia</v>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>supermarmo opaco, metallo</v>
       </c>
       <c r="G92" t="str">
         <v>tavolo, madeira, tavoli, mesa, mesas, table, comedor, dall, piano, cristallo, lucido, supermarmo, armonioso, intreccio, archi, definisce, unico, protagonista</v>
@@ -6073,13 +6346,13 @@
         <v>88-open</v>
       </c>
       <c r="K92">
-        <v>62</v>
+        <v>61.4</v>
       </c>
       <c r="L92">
-        <v>-30</v>
+        <v>-28.6</v>
       </c>
       <c r="M92">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="N92" t="str">
         <v>BOX 640 - B_644</v>
@@ -6097,15 +6370,18 @@
         <v>TRUE</v>
       </c>
       <c r="S92" t="str">
-        <v/>
+        <v>rotondo o ovale, fisso o allungabile</v>
       </c>
       <c r="T92" t="str">
+        <v>Contemporaneo, Classico elegante</v>
+      </c>
+      <c r="U92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>box-640-b-645-sedia-dea</v>
+        <v>FEB-092</v>
       </c>
       <c r="B93" t="str">
         <v>Sedia Dea</v>
@@ -6132,16 +6408,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J93" t="str">
-        <v>88-open</v>
+        <v>84</v>
       </c>
       <c r="K93">
-        <v>89</v>
+        <v>128.2</v>
       </c>
       <c r="L93">
-        <v>-47</v>
+        <v>-35.6</v>
       </c>
       <c r="M93">
-        <v>70</v>
+        <v>54.1</v>
       </c>
       <c r="N93" t="str">
         <v>BOX 640 - B_645</v>
@@ -6162,12 +6438,15 @@
         <v/>
       </c>
       <c r="T93" t="str">
+        <v>Classico elegante, Caldo accogliente</v>
+      </c>
+      <c r="U93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>box-660-b-664-tavolo-daniel</v>
+        <v>FEB-093</v>
       </c>
       <c r="B94" t="str">
         <v>Tavolo Daniel</v>
@@ -6197,13 +6476,13 @@
         <v>91</v>
       </c>
       <c r="K94">
-        <v>69</v>
+        <v>74.8</v>
       </c>
       <c r="L94">
-        <v>-31</v>
+        <v>-29</v>
       </c>
       <c r="M94">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="N94" t="str">
         <v>BOX 660 - B_664</v>
@@ -6224,12 +6503,15 @@
         <v/>
       </c>
       <c r="T94" t="str">
+        <v>Classico elegante</v>
+      </c>
+      <c r="U94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>box-660-b-665-sedia-dea</v>
+        <v>FEB-094</v>
       </c>
       <c r="B95" t="str">
         <v>Sedia Dea</v>
@@ -6241,10 +6523,10 @@
         <v>La sedia Dea è perfetta per progetti raffinati in ogni dettaglio. La linearità delle gambe in metallo verniciato disponibile nelle finiture Ottone scuro, Antracite, Nero e Sabbia è ammorbidita dalle forme curve e accoglienti della seduta e dello schienale, arricchite da un prezioso tocco sartoriale che si rivela con il grazioso movimento di pieghe che enfatizza i volumi e il senso di comfort. Dea è una sedia di valore che cattura inevitabilmente l'ammirazione di chiunque la osservi.</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>tortora</v>
       </c>
       <c r="F95" t="str">
-        <v/>
+        <v>tessuto</v>
       </c>
       <c r="G95" t="str">
         <v>sedia, dea, sedie, silla, sillas, chair, asiento, perfetta, progetti, raffinati, ogni, dettaglio, linearita, gambe, metallo, verniciato, disponibile, nelle</v>
@@ -6259,13 +6541,13 @@
         <v>91</v>
       </c>
       <c r="K95">
-        <v>121</v>
+        <v>131.4</v>
       </c>
       <c r="L95">
-        <v>-33</v>
+        <v>-4.6</v>
       </c>
       <c r="M95">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="N95" t="str">
         <v>BOX 660 - B_665</v>
@@ -6286,12 +6568,15 @@
         <v/>
       </c>
       <c r="T95" t="str">
-        <v/>
+        <v>Classico elegante, Caldo accogliente</v>
+      </c>
+      <c r="U95" t="str">
+        <v>Nero</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>box-660-b-667-boiserie</v>
+        <v>FEB-095</v>
       </c>
       <c r="B96" t="str">
         <v>Boiserie</v>
@@ -6318,16 +6603,16 @@
         <v>GALLERIA</v>
       </c>
       <c r="J96" t="str">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K96">
-        <v>25</v>
+        <v>132.6</v>
       </c>
       <c r="L96">
-        <v>10</v>
+        <v>-13.4</v>
       </c>
       <c r="M96">
-        <v>70</v>
+        <v>80.2</v>
       </c>
       <c r="N96" t="str">
         <v>BOX 660 - B_667</v>
@@ -6348,12 +6633,405 @@
         <v/>
       </c>
       <c r="T96" t="str">
+        <v>Contemporaneo</v>
+      </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>FEB-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Armadio Profile/ Leather</v>
+      </c>
+      <c r="C97" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="D97" t="str">
+        <v>L'armadio con anta battente Profile Leather di Febal Casa combina eleganza materica e funzionalità per un arredo raffinato.</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>armadio, profile/, leather, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, battente, profile, febal, casa, combina, eleganza, materica, funzionalita, arredo</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>CASA 01 - AUTENTICA</v>
+      </c>
+      <c r="J97" t="str">
+        <v>38</v>
+      </c>
+      <c r="K97">
+        <v>7</v>
+      </c>
+      <c r="L97">
+        <v>1.7</v>
+      </c>
+      <c r="M97">
+        <v>65.6</v>
+      </c>
+      <c r="N97" t="str">
+        <v>BOX 180 - B_192</v>
+      </c>
+      <c r="O97" t="str">
+        <v>assets/febal-casa/placeholder-product.png</v>
+      </c>
+      <c r="P97" t="str">
+        <v>https://www.febalcasa.com/it/tipologia/armadi/ante/battente/profile-leather/</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="R97" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>FEB-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Cabina Armadio Telaio</v>
+      </c>
+      <c r="C98" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Una cabina armadio dal design architettonico, con struttura in metallo e pannelli in vetro per un guardaroba con effetto leggero e luminoso.</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>cabina, armadio, telaio, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, design, architettonico, struttura, metallo, pannelli, vetro, guardaroba, effetto, leggero, luminoso</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v>CASA 01 - AUTENTICA</v>
+      </c>
+      <c r="J98" t="str">
+        <v>38</v>
+      </c>
+      <c r="K98">
+        <v>83.8</v>
+      </c>
+      <c r="L98">
+        <v>-1.3</v>
+      </c>
+      <c r="M98">
+        <v>65.5</v>
+      </c>
+      <c r="N98" t="str">
+        <v>BOX 180 - B_193</v>
+      </c>
+      <c r="O98" t="str">
+        <v>assets/febal-casa/products/telaio.jpg</v>
+      </c>
+      <c r="P98" t="str">
+        <v>https://www.febalcasa.com/it/tipologia/cabine-armadio/telaio/</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="R98" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FEB-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Cassettiera Square</v>
+      </c>
+      <c r="C99" t="str">
+        <v>cassettiere</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Cassettiera Square — elemento della collezione Febal Casa, sezione CASA 01 - AUTENTICA.</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>cassettiera, square, cassettiere, comoda, cómoda, cómodas, cajonera, dresser, casa, elemento, collezione, febal, sezione, autentica</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v>CASA 01 - AUTENTICA</v>
+      </c>
+      <c r="J99" t="str">
+        <v>36</v>
+      </c>
+      <c r="K99">
+        <v>-14.1</v>
+      </c>
+      <c r="L99">
+        <v>-49</v>
+      </c>
+      <c r="M99">
+        <v>108.6</v>
+      </c>
+      <c r="N99" t="str">
+        <v>BOX 180 - B_194</v>
+      </c>
+      <c r="O99" t="str">
+        <v>assets/febal-casa/products/square.jpg</v>
+      </c>
+      <c r="P99" t="str">
+        <v>https://www.febalcasa.com/it/tipologia/armadi/cassettiere/square/</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>cassettiere</v>
+      </c>
+      <c r="R99" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FEB-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Armadio Barret con Portale</v>
+      </c>
+      <c r="C100" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Scopri gli armadi a ponte con passaggio Febal Casa: soluzioni architettoniche che ottimizzano lo spazio con stile e funzionalità.</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>armadio, barret, portale, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, scopri, ponte, passaggio, febal, casa, soluzioni, architettoniche, ottimizzano, spazio, stile, funzionalita</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v>CASA 01 - AUTENTICA</v>
+      </c>
+      <c r="J100" t="str">
+        <v>33</v>
+      </c>
+      <c r="K100">
+        <v>38.1</v>
+      </c>
+      <c r="L100">
+        <v>-0.9</v>
+      </c>
+      <c r="M100">
+        <v>119.2</v>
+      </c>
+      <c r="N100" t="str">
+        <v>BOX 190 - B_191</v>
+      </c>
+      <c r="O100" t="str">
+        <v>assets/febal-casa/placeholder-product.png</v>
+      </c>
+      <c r="P100" t="str">
+        <v>https://www.febalcasa.com/it/tipologia/armadi/ispirazioni/armadio-con-passaggio-con-ponte/</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="R100" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FEB-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Armadio Halley</v>
+      </c>
+      <c r="C101" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="D101" t="str">
+        <v>L’armadio con anta scorrevole Halley gioca sui contrasti cromatici e materici esaltati dalla luce led integrata che unisce efficacia ed estetica.</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>armadio, halley, armadi, armario, armarios, closet, ropero, wardrobe, cabina armadio, vestidor, anta, scorrevole, gioca, contrasti, cromatici, materici, esaltati, luce, integrata, unisce</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v>CASA 03 - AUDACE</v>
+      </c>
+      <c r="J101" t="str">
+        <v>47</v>
+      </c>
+      <c r="K101">
+        <v>-151.8</v>
+      </c>
+      <c r="L101">
+        <v>-4.3</v>
+      </c>
+      <c r="M101">
+        <v>130</v>
+      </c>
+      <c r="N101" t="str">
+        <v>BOX 340 - B_341</v>
+      </c>
+      <c r="O101" t="str">
+        <v>assets/febal-casa/products/halley.jpg</v>
+      </c>
+      <c r="P101" t="str">
+        <v>https://www.febalcasa.com/it/prodotti/febal-notte-armadio-scorrevole-halley-01/</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>armadi</v>
+      </c>
+      <c r="R101" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FEB-101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Letto Arden</v>
+      </c>
+      <c r="C102" t="str">
+        <v>camera da letto</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Allure di Febal Casa: letto imbottito con testata dalle linee verticali che evocano il fusto di una colonna. Discrezione e carattere per la camera da letto matrimoniale.</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>letto, arden, camera da letto, cama, dormitorio, bed, recamara, recámara, habitacion, gruppo notte, allure, febal, casa, imbottito, testata, linee, verticali, evocano, fusto, colonna, discrezione</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v>CASA 03 - AUDACE</v>
+      </c>
+      <c r="J102" t="str">
+        <v>46</v>
+      </c>
+      <c r="K102">
+        <v>144.3</v>
+      </c>
+      <c r="L102">
+        <v>-36.6</v>
+      </c>
+      <c r="M102">
+        <v>91.6</v>
+      </c>
+      <c r="N102" t="str">
+        <v>BOX 340 - B_343</v>
+      </c>
+      <c r="O102" t="str">
+        <v>assets/febal-casa/products/allure.jpg</v>
+      </c>
+      <c r="P102" t="str">
+        <v>https://www.febalcasa.com/it/prodotti/allure/</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>camera-da-letto</v>
+      </c>
+      <c r="R102" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U102"/>
   </ignoredErrors>
 </worksheet>
 </file>